--- a/sources/jack2_step8.xlsx
+++ b/sources/jack2_step8.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB105"/>
+  <dimension ref="A1:AB107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" min="1" max="1"/>
@@ -3956,12 +3956,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>db+1,1,1,[1,1],2</t>
+          <t>db+1,1,1,2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>db+1,1,1,[1,1],2</t>
+          <t>db+1,1,1,2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3986,273 +3986,288 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-6 -6 -6 -6 -11 -16</t>
+          <t>-6 -6 -11 -16</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-6 -6 -6 -6 -11 -16</t>
+          <t>-6 -6 -11 -16</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>+5 +5 +5 +5 0 KD</t>
+          <t>+5 +5 0 KD</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+5 +5 +5 +5 0 KD</t>
+          <t>+5 +5 0 KD</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>+5 +5 +5 +5 0 KD</t>
+          <t>+5 +5 0 KD</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>+5 +5 +5 +5 0 KD</t>
+          <t>+5 +5 0 KD</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>12,15,15,15,15,40</t>
+          <t>12,15,15,40</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>12,15,15,15,15,40</t>
+          <t>12,15,15,40</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>lllllm</t>
+          <t>lllm</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>lllllm</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>lllm</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>4cf7be1b-11d0-4c05-8424-e597df98603b</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>7cab04d2-5592-467a-bea7-99322350b7b3</t>
+          <t>dc5a29f5-7ecb-4a43-967e-7b5eadf20512</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>b,db,d,DF+1</t>
+          <t>db+1,1,1,1,2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>b,db,d,DF+1</t>
+          <t>db+1,1,1,1,2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Debugger</t>
+          <t>Machine Gun - Megaton Punch</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Debugger</t>
+          <t>Machine Gun - Megaton Punch</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-45</t>
+          <t>-6 -6 -6 -11 -16</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-45</t>
+          <t>-6 -6 -6 -11 -16</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +5 +5 0 KD</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +5 +5 0 KD</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +5 +5 0 KD</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +5 +5 0 KD</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12,15,15,15,40</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>97</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12,15,15,15,40</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>llllm</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>llllm</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>85158165-351f-41d2-8735-2ab0b63af148</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>2747e1e2-0cb3-4730-81ad-dc7a7427a2b6</t>
+          <t>b3cad2bc-95a3-4d7c-9abb-0335ed57fb7d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>hcf</t>
+          <t>db+1,1,1,1,1,2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>hcf</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>b,b+1</t>
+          <t>db+1,1,1,1,1,2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Wind Up</t>
+          <t>Machine Gun - Megaton Punch</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wind Up</t>
+          <t>Machine Gun - Megaton Punch</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>-6 -6 -6 -6 -11 -16</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>-6 -6 -6 -6 -11 -16</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>+5 +5 +5 +5 0 KD</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>+5 +5 +5 +5 0 KD</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>+5 +5 +5 +5 0 KD</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>+5 +5 +5 +5 0 KD</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12,15,15,15,15,40</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12,15,15,15,15,40</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>lllllm</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>lllllm</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>c03fb65b-aaac-4006-8e2b-0a9f8c08fd8f</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>1a0aed99-b547-48d7-925a-8f99bbeb0917</t>
+          <t>3a6ce42c-3b05-4641-9152-428a8ed9fd0f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>– 1</t>
+          <t>b,db,d,DF+1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>hcf,1</t>
+          <t>b,db,d,DF+1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Gigaton Punch</t>
+          <t>Debugger</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Wind Up – Gigaton Punch</t>
+          <t>Debugger</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>23</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>+21</t>
+          <t>-45</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>+21</t>
+          <t>-45</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4277,798 +4292,758 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>-,20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>L</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>-m</t>
+          <t>L</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2003590c-d918-44b9-ba39-ae204bd6ae62</t>
+          <t>85158165-351f-41d2-8735-2ab0b63af148</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>4b654016-9d3d-4588-aaf3-bcba06d600eb</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>c03fb65b-aaac-4006-8e2b-0a9f8c08fd8f</t>
+          <t>2747e1e2-0cb3-4730-81ad-dc7a7427a2b6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>– DF+1</t>
+          <t>hcf</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>hcf,DF+1</t>
+          <t>hcf</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>b,b+1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Debugger</t>
+          <t>Wind Up</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Wind Up – Debugger</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>-45</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>-45</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>KD</t>
+          <t>Wind Up</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>-,25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>-L</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>bfcd8070-9fe9-4f68-b19e-bddec360b30a</t>
+          <t>c03fb65b-aaac-4006-8e2b-0a9f8c08fd8f</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>bc7743df-d62c-4baf-90d6-ca367a954aba</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>c03fb65b-aaac-4006-8e2b-0a9f8c08fd8f</t>
+          <t>1a0aed99-b547-48d7-925a-8f99bbeb0917</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DF+1,2,1,2</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DF+1,2,1,2</t>
+          <t>hcf,1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Uppercut Rush</t>
+          <t>Gigaton Punch</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Uppercut Rush</t>
+          <t>Wind Up – Gigaton Punch</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>14</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-11 -7 -9 -2</t>
+          <t>+21</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>-11 -7 -9 -2</t>
+          <t>+21</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>KD +4 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>KD +4 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>KD +4 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>KD +4 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>10,15,10,15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>10,15,10,15</t>
+          <t>-,20</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>mmmm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>mmmm</t>
+          <t>-m</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>JGc RC</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Juggles on the last hit if the first hit was a counter hit.</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>4f881878-519e-4f9f-bb13-ebe8511b7e9f</t>
+          <t>2003590c-d918-44b9-ba39-ae204bd6ae62</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>bf72dea8-4c41-4bb6-9420-9305240a53e3</t>
+          <t>4b654016-9d3d-4588-aaf3-bcba06d600eb</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>c03fb65b-aaac-4006-8e2b-0a9f8c08fd8f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Df+1,2,1</t>
+          <t>– DF+1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Df+1,2,1</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>FC+DF+1,2,1</t>
+          <t>hcf,DF+1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Quick Upper Rush</t>
+          <t>Debugger</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Quick Upper Rush</t>
+          <t>Wind Up – Debugger</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-6 -8 -2</t>
+          <t>-45</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>-6 -8 -2</t>
+          <t>-45</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>+5 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>+5 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>+5 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>+5 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>15,12,15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>15,12,15</t>
+          <t>-,25</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>L</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>-L</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>JGc RC</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Juggles on the last hit if the first hit was a counter hit.</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>7507a693-7948-45eb-a05e-3707d923e16d</t>
+          <t>bfcd8070-9fe9-4f68-b19e-bddec360b30a</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>b30faab6-54e4-4123-ab0b-5fb12faa3be2</t>
+          <t>bc7743df-d62c-4baf-90d6-ca367a954aba</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>c03fb65b-aaac-4006-8e2b-0a9f8c08fd8f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FC+df+1,2,1</t>
+          <t>DF+1,2,1,2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FC+df+1,2,1</t>
+          <t>DF+1,2,1,2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Windmill</t>
+          <t>Uppercut Rush</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Windmill</t>
+          <t>Uppercut Rush</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-22 -22 -2</t>
+          <t>-11 -7 -9 -2</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-22 -22 -2</t>
+          <t>-11 -7 -9 -2</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>-12 -12 -12</t>
+          <t>KD +4 +2 +9</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-12 -12 -12</t>
+          <t>KD +4 +2 +9</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>-12 -12 -12</t>
+          <t>KD +4 +2 +9</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>-12 -12 -12</t>
+          <t>KD +4 +2 +9</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>10,15,10</t>
+          <t>10,15,10,15</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>50</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>10,15,10</t>
+          <t>10,15,10,15</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>mmmm</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>mmmm</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>JGc RC</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Juggles on the last hit if the first hit was a counter hit.</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>dbb96ec3-9f0f-4e57-b4ca-8de7e5046661</t>
+          <t>4f881878-519e-4f9f-bb13-ebe8511b7e9f</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>1c7f46c4-6ab3-4fdd-90e3-5f642409d3af</t>
+          <t>bf72dea8-4c41-4bb6-9420-9305240a53e3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>– 1</t>
+          <t>Df+1,2,1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FC+df+1,2,1,1</t>
+          <t>Df+1,2,1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>FC+DF+1,2,1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>– Windmill Backhand</t>
+          <t>Quick Upper Rush</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Windmill – Windmill Backhand</t>
+          <t>Quick Upper Rush</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>+20</t>
+          <t>-6 -8 -2</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>-22 -22 -2 +20</t>
+          <t>-6 -8 -2</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +2 +9</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-12 -12 -12 KD</t>
+          <t>+5 +2 +9</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +2 +9</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>-12 -12 -12 KD</t>
+          <t>+5 +2 +9</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15,12,15</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>42</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>10,15,10,30</t>
+          <t>15,12,15</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>mmmh</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>CF GB</t>
+          <t>JGc RC</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Juggles on the last hit if the first hit was a counter hit.</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>82838a4d-d558-42b7-ab73-e05d17ef4b08</t>
+          <t>7507a693-7948-45eb-a05e-3707d923e16d</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>e3e5f6b7-4929-4a52-8c31-e6806f1334ee</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>dbb96ec3-9f0f-4e57-b4ca-8de7e5046661</t>
+          <t>b30faab6-54e4-4123-ab0b-5fb12faa3be2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Df+1,2</t>
+          <t>FC+df+1,2,1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Df+1,2</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>FC+DF+1,2</t>
+          <t>FC+df+1,2,1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Medium Hammer Rush</t>
+          <t>Windmill</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Medium Hammer Rush</t>
+          <t>Windmill</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-6 -8</t>
+          <t>-22 -22 -2</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>-6 -8</t>
+          <t>-22 -22 -2</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>+5 +2</t>
+          <t>-12 -12 -12</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>+5 +2</t>
+          <t>-12 -12 -12</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>+5 +2</t>
+          <t>-12 -12 -12</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>+5 +2</t>
+          <t>-12 -12 -12</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>15,12</t>
+          <t>10,15,10</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>35</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>15,12</t>
+          <t>10,15,10</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
+          <t>dbb96ec3-9f0f-4e57-b4ca-8de7e5046661</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>53b77124-e72d-4f20-ae78-8225f04ac648</t>
+          <t>1c7f46c4-6ab3-4fdd-90e3-5f642409d3af</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>– d+1</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Df+1,2,d+1</t>
+          <t>FC+df+1,2,1,1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>– Low Punch</t>
+          <t>– Windmill Backhand</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Medium Hammer Rush – Low Punch</t>
+          <t>Windmill – Windmill Backhand</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>+20</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-6 -8 -17</t>
+          <t>-22 -22 -2 +20</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>+5 +2 -7</t>
+          <t>-12 -12 -12 KD</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>+5 +2 -7</t>
+          <t>-12 -12 -12 KD</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>15,12,8</t>
+          <t>10,15,10,30</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>h</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>mmL</t>
+          <t>mmmh</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>CF GB</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>29dfa2dc-0160-4e71-b110-03e973136272</t>
+          <t>82838a4d-d558-42b7-ab73-e05d17ef4b08</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>be700e61-7fed-40b2-a16a-4b062cedd1c9</t>
+          <t>e3e5f6b7-4929-4a52-8c31-e6806f1334ee</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
+          <t>dbb96ec3-9f0f-4e57-b4ca-8de7e5046661</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>– df+1</t>
+          <t>Df+1,2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Df+1,2,df+1</t>
+          <t>Df+1,2</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>FC+DF+1,2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>– Mid Punch</t>
+          <t>Medium Hammer Rush</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Medium Hammer Rush – Mid Punch</t>
+          <t>Medium Hammer Rush</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5078,57 +5053,57 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-6 -8</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-6 -8 -1</t>
+          <t>-6 -8</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+5 +2</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>+5 +2 +10</t>
+          <t>+5 +2</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+5 +2</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>+5 +2 +10</t>
+          <t>+5 +2</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>15,12</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>15,12,15</t>
+          <t>15,12</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5138,39 +5113,34 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>eb9bbfe4-68c3-4e58-baf7-821687138e91</t>
+          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>636b5aa8-46de-464e-81e9-d0bcfa43dc73</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
+          <t>53b77124-e72d-4f20-ae78-8225f04ac648</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>– f+1</t>
+          <t>– d+1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Df+1,2,f+1</t>
+          <t>Df+1,2,d+1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>– High Punch</t>
+          <t>– Low Punch</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Medium Hammer Rush – High Punch</t>
+          <t>Medium Hammer Rush – Low Punch</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5190,57 +5160,62 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>+5 +2 -5</t>
+          <t>+5 +2 -7</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>+5 +2 -5</t>
+          <t>+5 +2 -7</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>15,12,12</t>
+          <t>15,12,8</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>L</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>mmh</t>
+          <t>mmL</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>897a7dd1-1093-48ff-85f1-bebca88601ea</t>
+          <t>29dfa2dc-0160-4e71-b110-03e973136272</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>96ffff19-8555-4463-82fe-458f7c0c053b</t>
+          <t>be700e61-7fed-40b2-a16a-4b062cedd1c9</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -5252,87 +5227,82 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FC+1,1,1,2</t>
+          <t>– df+1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FC+1,1,1,2</t>
+          <t>Df+1,2,df+1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Hammer Rush</t>
+          <t>– Mid Punch</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hammer Rush</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>19</t>
+          <t>Medium Hammer Rush – Mid Punch</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>-8 +1 -12 -8</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>-8 +1 -12 -8</t>
+          <t>-6 -8 -1</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1</t>
+          <t>+5 +2 +10</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1</t>
+          <t>+5 +2 +10</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>10,8,12,12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>10,8,12,12</t>
+          <t>15,12,15</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>LLmm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>LLmm</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -5342,39 +5312,44 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
+          <t>eb9bbfe4-68c3-4e58-baf7-821687138e91</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>87b157c8-bac6-4b55-a543-03b3e5c1c00f</t>
+          <t>636b5aa8-46de-464e-81e9-d0bcfa43dc73</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>– d+1</t>
+          <t>– f+1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FC+1,1,1,2,d+1</t>
+          <t>Df+1,2,f+1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>– Low Punch</t>
+          <t>– High Punch</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hammer Rush – Low Punch</t>
+          <t>Medium Hammer Rush – High Punch</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5384,94 +5359,94 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>-8 +1 -12 -8 -17</t>
+          <t>-6 -8 -17</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1 -7</t>
+          <t>+5 +2 -5</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1 -7</t>
+          <t>+5 +2 -5</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>10,8,12,12,8</t>
+          <t>15,12,12</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>h</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>LLmmL</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>mmh</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>acb95787-cedc-4b5b-b8fb-50a3e72d4b5b</t>
+          <t>897a7dd1-1093-48ff-85f1-bebca88601ea</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>19e50734-0a3e-439a-bb45-d0541eae3da2</t>
+          <t>96ffff19-8555-4463-82fe-458f7c0c053b</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
+          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>– df+1</t>
+          <t>FC+1,1,1,2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FC+1,1,1,2,df+1</t>
+          <t>FC+1,1,1,2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>– Mid Punch</t>
+          <t>Hammer Rush</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hammer Rush – Mid Punch</t>
+          <t>Hammer Rush</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>19</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5481,57 +5456,57 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-8 +1 -12 -8</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>-8 +1 -12 -8 -1</t>
+          <t>-8 +1 -12 -8</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+2 +12 -1 +1</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1 +10</t>
+          <t>+2 +12 -1 +1</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+2 +12 -1 +1</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1 +10</t>
+          <t>+2 +12 -1 +1</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10,8,12,12</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>42</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>10,8,12,12,15</t>
+          <t>10,8,12,12</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>LLmm</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>LLmmm</t>
+          <t>LLmm</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -5541,39 +5516,34 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>756e1d64-081b-4d25-aaa0-fa5c3b7a738f</t>
+          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>ecd60ebe-4c07-4ca2-a44b-3748905360dd</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
+          <t>87b157c8-bac6-4b55-a543-03b3e5c1c00f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>– f+1</t>
+          <t>– d+1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FC+1,1,1,2,f+1</t>
+          <t>FC+1,1,1,2,d+1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>– High Punch</t>
+          <t>– Low Punch</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hammer Rush – High Punch</t>
+          <t>Hammer Rush – Low Punch</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5593,57 +5563,62 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1 -5</t>
+          <t>+2 +12 -1 +1 -7</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1 -5</t>
+          <t>+2 +12 -1 +1 -7</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>10,8,12,12,12</t>
+          <t>10,8,12,12,8</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>L</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>LLmmh</t>
+          <t>LLmmL</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>ac1b3ebe-7028-47a0-be65-5eb121dab8bc</t>
+          <t>acb95787-cedc-4b5b-b8fb-50a3e72d4b5b</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>fe5b804b-6426-463e-b283-4eb22f9998b3</t>
+          <t>19e50734-0a3e-439a-bb45-d0541eae3da2</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -5655,87 +5630,82 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FC+1,2</t>
+          <t>– df+1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FC+1,2</t>
+          <t>FC+1,1,1,2,df+1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Low Punch - Megaton Punch</t>
+          <t>– Mid Punch</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Low Punch - Megaton Punch</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
+          <t>Hammer Rush – Mid Punch</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-8 -14</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>-8 -14</t>
+          <t>-8 +1 -12 -8 -1</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>+2 KD</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>+2 KD</t>
+          <t>+2 +12 -1 +1 +10</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>+2 KD</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>+2 KD</t>
+          <t>+2 +12 -1 +1 +10</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>10,25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>10,25</t>
+          <t>10,8,12,12,15</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>Lm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>Lm</t>
+          <t>LLmmm</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -5745,141 +5715,136 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>06ab7954-5d39-49cc-91e3-02c54893dd53</t>
+          <t>756e1d64-081b-4d25-aaa0-fa5c3b7a738f</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>a769fb07-8a59-436e-a5fb-3acd34e8e01d</t>
+          <t>ecd60ebe-4c07-4ca2-a44b-3748905360dd</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SS+1</t>
+          <t>– f+1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SS+1</t>
+          <t>FC+1,1,1,2,f+1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Jack Hammer</t>
+          <t>– High Punch</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Jack Hammer</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>32</t>
+          <t>Hammer Rush – High Punch</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-8 +1 -12 -8 -17</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2 +12 -1 +1 -5</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2 +12 -1 +1 -5</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10,8,12,12,12</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>h</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>BN GB</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>LLmmh</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>41456c1a-f3a2-468f-b0ee-ee2032bb78c8</t>
+          <t>ac1b3ebe-7028-47a0-be65-5eb121dab8bc</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>de86a0e0-55fd-41e5-a239-a7685c39edbd</t>
+          <t>fe5b804b-6426-463e-b283-4eb22f9998b3</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SS+1+2</t>
+          <t>FC+1,2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SS+1+2</t>
+          <t>FC+1,2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Double Knuckle Swing</t>
+          <t>Low Punch - Megaton Punch</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Double Knuckle Swing</t>
+          <t>Low Punch - Megaton Punch</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5894,293 +5859,298 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-8 -14</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-8 -14</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2 KD</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2 KD</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2 KD</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2 KD</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
+          <t>10,25</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10,25</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>Lm</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>Lm</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>15c368e0-8f76-42a0-bbea-ef3cc510e19c</t>
+          <t>06ab7954-5d39-49cc-91e3-02c54893dd53</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>2f8a7e04-7a60-430d-bc0a-6a55ed0d3427</t>
+          <t>a769fb07-8a59-436e-a5fb-3acd34e8e01d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1+2&lt;1+2</t>
+          <t>SS+1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1+2&lt;1+2</t>
+          <t>SS+1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Hammer Knuckle - Double Uppercut</t>
+          <t>Jack Hammer</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hammer Knuckle - Double Uppercut</t>
+          <t>Jack Hammer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-15 -20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>-15 -20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>21,22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>21,22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>BN GB</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>54667fc1-c443-4001-a9d7-46c1d391bc4d</t>
+          <t>41456c1a-f3a2-468f-b0ee-ee2032bb78c8</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>36af744c-98c3-48c0-bea9-c96c61093c26</t>
+          <t>de86a0e0-55fd-41e5-a239-a7685c39edbd</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>WS+1+2&lt;1+2</t>
+          <t>SS+1+2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>WS+1+2&lt;1+2</t>
+          <t>SS+1+2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Double Uppercut - Hammer Knuckle</t>
+          <t>Double Knuckle Swing</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Double Uppercut - Hammer Knuckle</t>
+          <t>Double Knuckle Swing</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>-15 -16</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>-15 -16</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>21,17</t>
+          <t>35</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>21,17</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>h</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>JG</t>
+          <t>h</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>14470b5f-e125-4262-857b-20fa6db24ee3</t>
+          <t>15c368e0-8f76-42a0-bbea-ef3cc510e19c</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>45985eea-a458-447f-9b9d-941ed088446a</t>
+          <t>2f8a7e04-7a60-430d-bc0a-6a55ed0d3427</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>f+1+2</t>
+          <t>1+2&lt;1+2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>f+1+2</t>
+          <t>1+2&lt;1+2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Arm Scissors</t>
+          <t>Hammer Knuckle - Double Uppercut</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Arm Scissors</t>
+          <t>Hammer Knuckle - Double Uppercut</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6195,114 +6165,119 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-15 -20</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-15 -20</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21,22</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>43</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21,22</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
+          <t>54667fc1-c443-4001-a9d7-46c1d391bc4d</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>f51b4cde-994c-422f-b3e6-3e932f7d87ff</t>
+          <t>36af744c-98c3-48c0-bea9-c96c61093c26</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>– 1+2</t>
+          <t>WS+1+2&lt;1+2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>f+1+2,1+2</t>
+          <t>WS+1+2&lt;1+2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>– Cross Cut Saw</t>
+          <t>Double Uppercut - Hammer Knuckle</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Arm Scissors – Cross Cut Saw</t>
+          <t>Double Uppercut - Hammer Knuckle</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-15 -16</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>-10 -14</t>
+          <t>-15 -16</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6312,7 +6287,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -6322,69 +6297,69 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21,17</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>38</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>17,15</t>
+          <t>21,17</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>acab70ca-8813-48c6-907e-58ba82b57685</t>
+          <t>14470b5f-e125-4262-857b-20fa6db24ee3</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>e7af4cd0-902b-4b89-9c43-ea9365bec42c</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
+          <t>45985eea-a458-447f-9b9d-941ed088446a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>– ~df+2</t>
+          <t>f+1+2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>f+1+2~df+2</t>
+          <t>f+1+2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>– Megaton Punch</t>
+          <t>Arm Scissors</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Arm Scissors – Megaton Punch</t>
+          <t>Arm Scissors</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6394,12 +6369,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>-10 -19</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6409,7 +6384,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6419,22 +6394,22 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>17,25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6444,69 +6419,59 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>773af138-28f0-48ff-9b0e-97e83d2d8d3f</t>
+          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>b671f9fe-a460-4157-8300-00379e99322d</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
+          <t>f51b4cde-994c-422f-b3e6-3e932f7d87ff</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>d+1+2</t>
+          <t>– 1+2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>d+1+2</t>
+          <t>f+1+2,1+2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Bravo Knuckle</t>
+          <t>– Cross Cut Saw</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bravo Knuckle</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>Arm Scissors – Cross Cut Saw</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>-10 -14</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -6516,99 +6481,89 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
+          <t>KD KD</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>17,15</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>l</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>JG GB</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>When tagging in Bryan Fury hit 2 to grab the opponent in mid air and do a Fisherman's Slam. Total damage is 21,21.</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>f79bf7d8-dcd1-4a58-883f-38e113a7b9e1</t>
+          <t>acab70ca-8813-48c6-907e-58ba82b57685</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>2ecc5ad9-b4ca-485a-884a-0301a91b3509</t>
+          <t>e7af4cd0-902b-4b89-9c43-ea9365bec42c</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FC+1+2</t>
+          <t>– ~df+2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FC+1+2</t>
+          <t>f+1+2~df+2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Cross Cut Saw</t>
+          <t>– Megaton Punch</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cross Cut Saw</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>21</t>
+          <t>Arm Scissors – Megaton Punch</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6618,7 +6573,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-10 -19</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -6628,42 +6583,42 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
+          <t>KD KD</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17,25</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>m</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -6673,661 +6628,681 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>23e71f4e-0ab8-4ddc-89c1-4b2fe81234cc</t>
+          <t>773af138-28f0-48ff-9b0e-97e83d2d8d3f</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>52606470-ef56-4c68-a311-9fe12c9a5f23</t>
+          <t>b671f9fe-a460-4157-8300-00379e99322d</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Df+2,1,2</t>
+          <t>d+1+2</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Df+2,1,2</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>FC+DF+2,1,2</t>
+          <t>d+1+2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Quick Uppercut Rush</t>
+          <t>Bravo Knuckle</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Quick Uppercut Rush</t>
+          <t>Bravo Knuckle</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>-9 -2 -9</t>
+          <t>-23</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>-9 -2 -9</t>
+          <t>-23</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>-2 +10 +2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>-2 +10 +2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>-2 +10 +2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>-2 +10 +2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>15,10,15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>15,10,15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>JGc RC</t>
+          <t>JG GB</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>Juggles on the last hit if the first hit was a counter hit.</t>
+          <t>When tagging in Bryan Fury hit 2 to grab the opponent in mid air and do a Fisherman's Slam. Total damage is 21,21.</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>38964142-4e38-457c-9a6d-9ef0fcf12cd4</t>
+          <t>f79bf7d8-dcd1-4a58-883f-38e113a7b9e1</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>8efe400a-6435-45e4-92f5-b9e1d4fd9595</t>
+          <t>2ecc5ad9-b4ca-485a-884a-0301a91b3509</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DF+2,1,2,1</t>
+          <t>FC+1+2</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DF+2,1,2,1</t>
+          <t>FC+1+2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Hammer Uppercut Rush</t>
+          <t>Cross Cut Saw</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Hammer Uppercut Rush</t>
+          <t>Cross Cut Saw</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>-11 -6 -9 -1</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>-11 -6 -9 -1</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>KD +5 +3 +10</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>KD +5 +3 +10</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>KD +5 +3 +10</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>KD +5 +3 +10</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>10,15,12,15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>10,15,12,15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>mmmm</t>
+          <t>l</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>mmmm</t>
+          <t>l</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>JG RC</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>f62fd939-223c-47b4-982b-aecff23cfca4</t>
+          <t>23e71f4e-0ab8-4ddc-89c1-4b2fe81234cc</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>e85a400e-73a4-495b-917a-82244da3681f</t>
+          <t>52606470-ef56-4c68-a311-9fe12c9a5f23</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>f,f+2</t>
+          <t>Df+2,1,2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>f,f+2</t>
+          <t>Df+2,1,2</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>FC+DF+2,1,2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Atomic Hook</t>
+          <t>Quick Uppercut Rush</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Atomic Hook</t>
+          <t>Quick Uppercut Rush</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-9 -2 -9</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-9 -2 -9</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 +10 +2</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 +10 +2</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 +10 +2</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 +10 +2</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>15,10,15</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>15,10,15</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>mmm</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>JGc RC</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Juggles on the last hit if the first hit was a counter hit.</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>e3ef4e95-cdea-4525-83df-74474e814b2a</t>
+          <t>38964142-4e38-457c-9a6d-9ef0fcf12cd4</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>e14fe285-946c-414b-88e4-d7e2f3af2745</t>
+          <t>8efe400a-6435-45e4-92f5-b9e1d4fd9595</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2,1,2</t>
+          <t>DF+2,1,2,1</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2,1,2</t>
+          <t>DF+2,1,2,1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Punch - Elbow - Uppercut</t>
+          <t>Hammer Uppercut Rush</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Punch - Elbow - Uppercut</t>
+          <t>Hammer Uppercut Rush</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>0 0 -15</t>
+          <t>-11 -6 -9 -1</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>0 0 -15</t>
+          <t>-11 -6 -9 -1</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>+7 +2 KD</t>
+          <t>KD +5 +3 +10</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>+7 +2 KD</t>
+          <t>KD +5 +3 +10</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>+7 +2 KD</t>
+          <t>KD +5 +3 +10</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>+7 +2 KD</t>
+          <t>KD +5 +3 +10</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>12,15,20</t>
+          <t>10,15,12,15</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>52</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>12,15,20</t>
+          <t>10,15,12,15</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>mmmm</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>mmmm</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>JG</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>JG RC</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>b51b9f18-a0d7-4234-b6c4-e0db8e729094</t>
+          <t>f62fd939-223c-47b4-982b-aecff23cfca4</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>06e4e99f-b024-4491-a080-43e24bdee8bc</t>
+          <t>e85a400e-73a4-495b-917a-82244da3681f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Df+2</t>
+          <t>f,f+2</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Df+2</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>FC+df+2</t>
+          <t>f,f+2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Short Hammer Rush</t>
+          <t>Atomic Hook</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Short Hammer Rush</t>
+          <t>Atomic Hook</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>h</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>h</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
+          <t>e3ef4e95-cdea-4525-83df-74474e814b2a</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>d79c3cf7-3a6f-4c0a-b31a-e35de47e6878</t>
+          <t>e14fe285-946c-414b-88e4-d7e2f3af2745</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>– d+1</t>
+          <t>2,1,2</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Df+2,d+1</t>
+          <t>2,1,2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>– Low Punch</t>
+          <t>Punch - Elbow - Uppercut</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Short Hammer Rush – Low Punch</t>
+          <t>Punch - Elbow - Uppercut</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>0 0 -15</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>-13 -17</t>
+          <t>0 0 -15</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>+7 +2 KD</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>-2 -7</t>
+          <t>+7 +2 KD</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>+7 +2 KD</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>-2 -7</t>
+          <t>+7 +2 KD</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12,15,20</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>47</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>10,8</t>
+          <t>12,15,20</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>mL</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>82744639-21bd-464e-acb0-fb430a833b71</t>
+          <t>b51b9f18-a0d7-4234-b6c4-e0db8e729094</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>da44dd7b-4cdb-4823-a817-06318a68273c</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
+          <t>06e4e99f-b024-4491-a080-43e24bdee8bc</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>– df+1</t>
+          <t>Df+2</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Df+2,df+1</t>
+          <t>Df+2</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>FC+df+2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>– Mid Punch</t>
+          <t>Short Hammer Rush</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Short Hammer Rush – Mid Punch</t>
+          <t>Short Hammer Rush</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7337,47 +7312,47 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>-13 -1</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>-2 +10</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>-2 +10</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>10,15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7387,7 +7362,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -7397,39 +7372,34 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>9cba188e-9985-4f96-83e4-7db5474781d2</t>
+          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>51f0fb87-39b1-45cd-ab41-c081312a5d9b</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
+          <t>d79c3cf7-3a6f-4c0a-b31a-e35de47e6878</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>– f+1</t>
+          <t>– d+1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Df+2,f+1</t>
+          <t>Df+2,d+1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>– High Punch</t>
+          <t>– Low Punch</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Short Hammer Rush – High Punch</t>
+          <t>Short Hammer Rush – Low Punch</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -7449,57 +7419,62 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>-2 -5</t>
+          <t>-2 -7</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>-2 -5</t>
+          <t>-2 -7</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>10,12</t>
+          <t>10,8</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>L</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>mh</t>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>9dd1c03f-e1e1-4e41-b91a-88df8054ec5c</t>
+          <t>82744639-21bd-464e-acb0-fb430a833b71</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>529ea903-bd1d-4081-ab74-eb6b82eaab94</t>
+          <t>da44dd7b-4cdb-4823-a817-06318a68273c</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -7511,77 +7486,72 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>b,db,d,DF+2</t>
+          <t>– df+1</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>b,db,d,DF+2</t>
+          <t>Df+2,df+1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Megaton Punch</t>
+          <t>– Mid Punch</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Megaton Punch</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>21</t>
+          <t>Short Hammer Rush – Mid Punch</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-13 -1</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 +10</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 +10</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>10,15</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7591,7 +7561,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -7601,136 +7571,136 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>56b1623c-ef98-42a3-be49-2ebc46462a0f</t>
+          <t>9cba188e-9985-4f96-83e4-7db5474781d2</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>e818b2a1-12e3-409b-8e48-4b059aaa76c0</t>
+          <t>51f0fb87-39b1-45cd-ab41-c081312a5d9b</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>f,f+3</t>
+          <t>– f+1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>f,f+3</t>
+          <t>Df+2,f+1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Granite Stomp</t>
+          <t>– High Punch</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Granite Stomp</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>Short Hammer Rush – High Punch</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>-13 -17</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 -5</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 -5</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10,12</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>h</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>mh</t>
         </is>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>ee6c0589-29fe-439a-8f69-242d8e6811f6</t>
+          <t>9dd1c03f-e1e1-4e41-b91a-88df8054ec5c</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>879d1a1f-95b2-4081-aa4b-dc74da0c13c6</t>
+          <t>529ea903-bd1d-4081-ab74-eb6b82eaab94</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>f+3+4</t>
+          <t>b,db,d,DF+2</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>f+3+4</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>FC+df+3+4</t>
+          <t>b,db,d,DF+2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Giga Shoulder Ram</t>
+          <t>Megaton Punch</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Giga Shoulder Ram</t>
+          <t>Megaton Punch</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -7745,12 +7715,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -7775,17 +7745,17 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>33</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>33</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>33</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -7798,1479 +7768,1589 @@
           <t>m</t>
         </is>
       </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>RC</t>
+        </is>
+      </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>20d7633a-2326-4494-84f9-0a235f1c2fe8</t>
+          <t>56b1623c-ef98-42a3-be49-2ebc46462a0f</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>b0da65f9-bf50-406e-8de8-7db02d0abb2c</t>
+          <t>e818b2a1-12e3-409b-8e48-4b059aaa76c0</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DB+3,4,3,4,3,4</t>
+          <t>f,f+3</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DB+3,4,3,4,3,4</t>
+          <t>f,f+3</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Cossack Kicks</t>
+          <t>Granite Stomp</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cossack Kicks</t>
+          <t>Granite Stomp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>-20 -22 -20 -22...</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>-20 -22 -20 -22...</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>-9 -11 -9 -11...</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>-9 -11 -9 -11...</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>-9 -11 -9 -11...</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>-9 -11 -9 -11...</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>18,12,10,12,12,12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>18,12,10,12,12,12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>LLLLLL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>LLLLLL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>674f6841-5fbb-4b15-865f-9ab351c1a0f0</t>
+          <t>ee6c0589-29fe-439a-8f69-242d8e6811f6</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>4c477a6b-86e6-43f8-911d-93481004b0b5</t>
+          <t>879d1a1f-95b2-4081-aa4b-dc74da0c13c6</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>uf+3+4</t>
+          <t>f+3+4</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>uf+3+4</t>
+          <t>f+3+4</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>FC+df+3+4</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Hip Press</t>
+          <t>Giga Shoulder Ram</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hip Press</t>
+          <t>Giga Shoulder Ram</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>-40</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>-40</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>-40</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>-40</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>m</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>If the Hip Press Misses the opponent, Jack-2 can chain into Sit Down extentions.</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>3be14565-e783-4db3-9168-bf98e290f21d</t>
+          <t>20d7633a-2326-4494-84f9-0a235f1c2fe8</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>ce4da910-2232-4be6-a896-136d900764e1</t>
+          <t>b0da65f9-bf50-406e-8de8-7db02d0abb2c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>DB+3,4,3,4,3,4</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>DB+3,4,3,4,3,4</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Cossack Kicks</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Cossack Kicks</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>-20 -22 -20 -22...</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>-20 -22 -20 -22...</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>-9 -11 -9 -11...</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>-9 -11 -9 -11...</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>-9 -11 -9 -11...</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>-9 -11 -9 -11...</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>18,12,10,12,12,12</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>18,12,10,12,12,12</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>LLLLLL</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>LLLLLL</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>674f6841-5fbb-4b15-865f-9ab351c1a0f0</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>4c477a6b-86e6-43f8-911d-93481004b0b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>uf+3+4</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>uf+3+4</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Hip Press</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Hip Press</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>-40</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>-40</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>-40</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>-40</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>If the Hip Press Misses the opponent, Jack-2 can chain into Sit Down extentions.</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>3be14565-e783-4db3-9168-bf98e290f21d</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>ce4da910-2232-4be6-a896-136d900764e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>3+4</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>3+4</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>Sit Down</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>Sit Down</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
+      <c r="O88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
+      <c r="P88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr">
+      <c r="Q88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr">
+      <c r="R88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
+      <c r="S88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
+      <c r="Y88" t="inlineStr">
         <is>
           <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
+      <c r="Z88" t="inlineStr">
         <is>
           <t>8ff726df-3bc4-4645-98be-c2fad557ee7d</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87">
+    <row r="89">
+      <c r="A89">
         <f>~3+4</f>
         <v/>
       </c>
-      <c r="B87">
+      <c r="B89">
         <f>~3+4</f>
         <v/>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>– Hop Hip Press</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>– Hop Hip Press</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t>-34</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>-34</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>-34</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t>-34</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr">
+      <c r="O89" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
+      <c r="P89" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr">
+      <c r="Q89" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr">
+      <c r="R89" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
+      <c r="S89" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="W87" t="inlineStr">
+      <c r="W89" t="inlineStr">
         <is>
           <t>If the Hip Press Misses the opponent, Jack-2 can chain into Sit Down extentions.</t>
         </is>
       </c>
-      <c r="Y87" t="inlineStr">
+      <c r="Y89" t="inlineStr">
         <is>
           <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
+      <c r="Z89" t="inlineStr">
         <is>
           <t>1f37a24d-750f-4851-a2b5-a6b9a1b4ed26</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>– B</t>
         </is>
       </c>
-      <c r="B88">
+      <c r="B90">
         <f>~3+4,B</f>
         <v/>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>– Roll Back</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>– Hop Hip Press – Roll Back</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>-34</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>-34</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
+      <c r="P90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr">
+      <c r="Q90" t="inlineStr">
         <is>
           <t>35,-</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr">
+      <c r="R90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
+      <c r="S90" t="inlineStr">
         <is>
           <t>M-</t>
         </is>
       </c>
-      <c r="Y88" t="inlineStr">
+      <c r="Y90" t="inlineStr">
         <is>
           <t>a96a391b-b0cf-493d-a205-6511f1e34903</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
+      <c r="Z90" t="inlineStr">
         <is>
           <t>4f15e677-cb84-4d03-b6d8-82c26255c1d9</t>
         </is>
       </c>
-      <c r="AA88" t="inlineStr">
+      <c r="AA90" t="inlineStr">
         <is>
           <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>– F</t>
         </is>
       </c>
-      <c r="B89">
+      <c r="B91">
         <f>~3+4,F</f>
         <v/>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>– Roll Forward</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>– Hop Hip Press – Roll Forward</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>-34</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
+      <c r="N91" t="inlineStr">
         <is>
           <t>-34</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr">
+      <c r="O91" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
+      <c r="P91" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr">
+      <c r="Q91" t="inlineStr">
         <is>
           <t>35,-</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr">
+      <c r="R91" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
+      <c r="S91" t="inlineStr">
         <is>
           <t>M-</t>
         </is>
       </c>
-      <c r="Y89" t="inlineStr">
+      <c r="Y91" t="inlineStr">
         <is>
           <t>df8e44d6-d84c-4ee6-8117-15cb0b65ceb6</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
+      <c r="Z91" t="inlineStr">
         <is>
           <t>0680a704-d8c9-47e5-91a9-98babe1c15af</t>
         </is>
       </c>
-      <c r="AA89" t="inlineStr">
+      <c r="AA91" t="inlineStr">
         <is>
           <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>– 1,2,1,2</t>
         </is>
       </c>
-      <c r="B90">
+      <c r="B92">
         <f>~3+4,1,2,1,2</f>
         <v/>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>– Sitting Punches</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>– Hop Hip Press – Sitting Punches</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>-45 -43 -45 -43</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>+3 -45 -43 -45 -43</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t>-35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t>-34 -35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>-35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
+      <c r="N92" t="inlineStr">
         <is>
           <t>-34 -35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr">
+      <c r="O92" t="inlineStr">
         <is>
           <t>10,10,10,10</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
+      <c r="P92" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr">
+      <c r="Q92" t="inlineStr">
         <is>
           <t>35,10,10,10,10</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr">
+      <c r="R92" t="inlineStr">
         <is>
           <t>llll</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
+      <c r="S92" t="inlineStr">
         <is>
           <t>Mllll</t>
         </is>
       </c>
-      <c r="Y90" t="inlineStr">
+      <c r="Y92" t="inlineStr">
         <is>
           <t>1e575213-1523-40b8-9492-0a92235d1799</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
+      <c r="Z92" t="inlineStr">
         <is>
           <t>71c8d35f-24b6-430d-abc5-2ff4c47a8f3b</t>
         </is>
       </c>
-      <c r="AA90" t="inlineStr">
+      <c r="AA92" t="inlineStr">
         <is>
           <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>KND d+1+2</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>KND d+1+2</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>Spring Hammer - Sit Down</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>Spring Hammer - Sit Down</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>+20</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>+20</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t>+14</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>+14</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>+14</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
+      <c r="N93" t="inlineStr">
         <is>
           <t>+14</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr">
+      <c r="O93" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="P93" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr">
+      <c r="Q93" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr">
+      <c r="R93" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
+      <c r="S93" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y91" t="inlineStr">
+      <c r="Y93" t="inlineStr">
         <is>
           <t>9ea7e1a3-859f-438a-b3fc-0ff0de0e315f</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
+      <c r="Z93" t="inlineStr">
         <is>
           <t>0066d9e6-44cc-4c22-b95a-1c01b1cb1dcb</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>– 1,2,1,2</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>KND d+1+2,1,2,1,2</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>– Sitting Punches</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>Spring Hammer - Sit Down – Sitting Punches</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>-45 -43 -45 -43</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>+20 -45 -43 -45 -43</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="K94" t="inlineStr">
         <is>
           <t>-35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t>+14 -35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t>-35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr">
+      <c r="N94" t="inlineStr">
         <is>
           <t>+14 -35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr">
+      <c r="O94" t="inlineStr">
         <is>
           <t>10,10,10,10</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
+      <c r="P94" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr">
+      <c r="Q94" t="inlineStr">
         <is>
           <t>12,10,10,10,10</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr">
+      <c r="R94" t="inlineStr">
         <is>
           <t>llll</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
+      <c r="S94" t="inlineStr">
         <is>
           <t>mllll</t>
         </is>
       </c>
-      <c r="Y92" t="inlineStr">
+      <c r="Y94" t="inlineStr">
         <is>
           <t>eb0c424e-d4b0-438e-bfb7-164bbca1894a</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
+      <c r="Z94" t="inlineStr">
         <is>
           <t>01e88eb2-b793-4ba3-9d87-7f7b3ab33381</t>
         </is>
       </c>
-      <c r="AA92" t="inlineStr">
+      <c r="AA94" t="inlineStr">
         <is>
           <t>9ea7e1a3-859f-438a-b3fc-0ff0de0e315f</t>
         </is>
       </c>
     </row>
-    <row r="93"/>
-    <row r="94">
-      <c r="A94" s="1" t="inlineStr">
+    <row r="95"/>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
         <is>
           <t>Unblockable Arts</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="1" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
+      <c r="B97" s="1" t="inlineStr">
         <is>
           <t>Command Full</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>Alt Commands</t>
         </is>
       </c>
-      <c r="D95" s="1" t="inlineStr">
+      <c r="D97" s="1" t="inlineStr">
         <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E95" s="1" t="inlineStr">
+      <c r="E97" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F95" s="1" t="inlineStr">
+      <c r="F97" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G95" s="1" t="inlineStr">
+      <c r="G97" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H95" s="1" t="inlineStr">
+      <c r="H97" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I95" s="1" t="inlineStr">
+      <c r="I97" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J95" s="1" t="inlineStr">
+      <c r="J97" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K95" s="1" t="inlineStr">
+      <c r="K97" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L95" s="1" t="inlineStr">
+      <c r="L97" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M95" s="1" t="inlineStr">
+      <c r="M97" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N95" s="1" t="inlineStr">
+      <c r="N97" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O95" s="1" t="inlineStr">
+      <c r="O97" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P95" s="1" t="inlineStr">
+      <c r="P97" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q95" s="1" t="inlineStr">
+      <c r="Q97" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R95" s="1" t="inlineStr">
+      <c r="R97" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S95" s="1" t="inlineStr">
+      <c r="S97" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T95" s="1" t="inlineStr">
+      <c r="T97" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U95" s="1" t="inlineStr">
+      <c r="U97" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V95" s="1" t="inlineStr">
+      <c r="V97" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W95" s="1" t="inlineStr">
+      <c r="W97" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X95" s="1" t="inlineStr">
+      <c r="X97" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y95" s="1" t="inlineStr">
+      <c r="Y97" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z95" s="1" t="inlineStr">
+      <c r="Z97" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA95" s="1" t="inlineStr">
+      <c r="AA97" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB95" s="1" t="inlineStr">
+      <c r="AB97" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>hcf</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>hcf</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>b,b+1</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Gigaton Start Up</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Gigaton Start Up</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>d1938783-b653-4c21-91d7-5303ce4b61cb</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>67a32d45-116c-42ad-88df-89b38e4ca9aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>– b,db,d,df,f,uf,u,ub</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>hcf,b,db,d,df,f,uf,u,ub</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>– Wind Up</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Gigaton Start Up – Wind Up</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>-,-</t>
-        </is>
-      </c>
-      <c r="R97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>Can be repeated up to 5 times.</t>
-        </is>
-      </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>1f65d946-be2a-4bb4-9a27-18e4ad27b7a8</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>99aa8796-5bbe-4d4a-8523-9278daf2c772</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>d1938783-b653-4c21-91d7-5303ce4b61cb</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
+          <t>hcf</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>hcf</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>b,b+1</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Gigaton Start Up</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Gigaton Start Up</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>d1938783-b653-4c21-91d7-5303ce4b61cb</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>67a32d45-116c-42ad-88df-89b38e4ca9aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>– b,db,d,df,f,uf,u,ub</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>hcf,b,db,d,df,f,uf,u,ub</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>– Wind Up</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Gigaton Start Up – Wind Up</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>-,-</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Can be repeated up to 5 times.</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>1f65d946-be2a-4bb4-9a27-18e4ad27b7a8</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>99aa8796-5bbe-4d4a-8523-9278daf2c772</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>d1938783-b653-4c21-91d7-5303ce4b61cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
           <t>–– 1</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>hcf,b,db,d,df,f,uf,u,ub,1</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>–– Gigaton Punch</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>Gigaton Start Up – Wind Up – Gigaton Punch</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="K100" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr">
+      <c r="N100" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr">
+      <c r="O100" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr">
+      <c r="P100" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr">
+      <c r="Q100" t="inlineStr">
         <is>
           <t>-,-,40</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr">
+      <c r="R100" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
+      <c r="S100" t="inlineStr">
         <is>
           <t>--!</t>
         </is>
       </c>
-      <c r="W98" t="inlineStr">
+      <c r="W100" t="inlineStr">
         <is>
           <t>Damage increases to 60, 80 and 199 with each extra Wind Up. Becomes Unblockable after 2 Wind Ups.</t>
         </is>
       </c>
-      <c r="Y98" t="inlineStr">
+      <c r="Y100" t="inlineStr">
         <is>
           <t>5effdb03-d23f-4671-8daa-b173c35d0ee4</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
+      <c r="Z100" t="inlineStr">
         <is>
           <t>8ae507ae-80ca-4f99-8564-71283564636c</t>
         </is>
       </c>
-      <c r="AA98" t="inlineStr">
+      <c r="AA100" t="inlineStr">
         <is>
           <t>1f65d946-be2a-4bb4-9a27-18e4ad27b7a8</t>
         </is>
       </c>
     </row>
-    <row r="99"/>
-    <row r="100">
-      <c r="A100" s="1" t="inlineStr">
+    <row r="101"/>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
         <is>
           <t>String Hit Arts</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="1" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
+      <c r="B103" s="1" t="inlineStr">
         <is>
           <t>Command Full</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>Alt Commands</t>
         </is>
       </c>
-      <c r="D101" s="1" t="inlineStr">
+      <c r="D103" s="1" t="inlineStr">
         <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E101" s="1" t="inlineStr">
+      <c r="E103" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F101" s="1" t="inlineStr">
+      <c r="F103" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G101" s="1" t="inlineStr">
+      <c r="G103" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H101" s="1" t="inlineStr">
+      <c r="H103" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I101" s="1" t="inlineStr">
+      <c r="I103" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J101" s="1" t="inlineStr">
+      <c r="J103" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K101" s="1" t="inlineStr">
+      <c r="K103" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L101" s="1" t="inlineStr">
+      <c r="L103" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M101" s="1" t="inlineStr">
+      <c r="M103" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N101" s="1" t="inlineStr">
+      <c r="N103" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O101" s="1" t="inlineStr">
+      <c r="O103" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P101" s="1" t="inlineStr">
+      <c r="P103" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q101" s="1" t="inlineStr">
+      <c r="Q103" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R101" s="1" t="inlineStr">
+      <c r="R103" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S101" s="1" t="inlineStr">
+      <c r="S103" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T101" s="1" t="inlineStr">
+      <c r="T103" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U101" s="1" t="inlineStr">
+      <c r="U103" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V101" s="1" t="inlineStr">
+      <c r="V103" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W101" s="1" t="inlineStr">
+      <c r="W103" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X101" s="1" t="inlineStr">
+      <c r="X103" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y101" s="1" t="inlineStr">
+      <c r="Y103" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z101" s="1" t="inlineStr">
+      <c r="Z103" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA101" s="1" t="inlineStr">
+      <c r="AA103" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB101" s="1" t="inlineStr">
+      <c r="AB103" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>D+2,1,1,1,2,1,2,1,1+2,1+2</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>D+2,1,1,1,2,1,2,1,1+2,1+2</t>
-        </is>
-      </c>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>10,6,5,7,7,6,6,8,21,25</t>
-        </is>
-      </c>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>10,6,5,7,7,6,6,8,21,25</t>
-        </is>
-      </c>
-      <c r="R102" t="inlineStr">
-        <is>
-          <t>sLLmmmmmmm</t>
-        </is>
-      </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>sLLmmmmmmm</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>cedd2a7b-61d7-42fe-9349-42a2b1503d3f</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>ML only</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>D+2,1,1,1,2,1,2,1,d+1+2,1+2</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>D+2,1,1,1,2,1,2,1,d+1+2,1+2</t>
-        </is>
-      </c>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t>10,6,5,7,7,6,6,8,12,35</t>
-        </is>
-      </c>
-      <c r="P103" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>10,6,5,7,7,6,6,8,12,35</t>
-        </is>
-      </c>
-      <c r="R103" t="inlineStr">
-        <is>
-          <t>sLLmmmmmlm</t>
-        </is>
-      </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>sLLmmmmmlm</t>
-        </is>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>46414757-6bbc-43ff-bcce-43bb3e815b75</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>ML only</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>uf+1,1,4,3,4,1,2,1,1+2,1+2</t>
+          <t>D+2,1,1,1,2,1,2,1,1+2,1+2</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>uf+1,1,4,3,4,1,2,1,1+2,1+2</t>
+          <t>D+2,1,1,1,2,1,2,1,1+2,1+2</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>15,8,5,5,5,8,6,8,21,25</t>
+          <t>10,6,5,7,7,6,6,8,21,25</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>101</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>15,8,5,5,5,8,6,8,21,25</t>
+          <t>10,6,5,7,7,6,6,8,21,25</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>hmLLLmmmmm</t>
+          <t>sLLmmmmmmm</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>hmLLLmmmmm</t>
+          <t>sLLmmmmmmm</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>66ed2d10-6ef0-489d-ad01-ab4680052d18</t>
+          <t>cedd2a7b-61d7-42fe-9349-42a2b1503d3f</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
@@ -9282,45 +9362,139 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>D+2,1,1,1,2,1,2,1,d+1+2,1+2</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>D+2,1,1,1,2,1,2,1,d+1+2,1+2</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>10,6,5,7,7,6,6,8,12,35</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>10,6,5,7,7,6,6,8,12,35</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>sLLmmmmmlm</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>sLLmmmmmlm</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>46414757-6bbc-43ff-bcce-43bb3e815b75</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>ML only</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>uf+1,1,4,3,4,1,2,1,1+2,1+2</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>uf+1,1,4,3,4,1,2,1,1+2,1+2</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>15,8,5,5,5,8,6,8,21,25</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>15,8,5,5,5,8,6,8,21,25</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>hmLLLmmmmm</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>hmLLLmmmmm</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>66ed2d10-6ef0-489d-ad01-ab4680052d18</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>ML only</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
           <t>uf+1,1,4,3,4,12,1,d+1+2,1+2</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>uf+1,1,4,3,4,12,1,d+1+2,1+2</t>
         </is>
       </c>
-      <c r="O105" t="inlineStr">
+      <c r="O107" t="inlineStr">
         <is>
           <t>15,8,5,5,5,8,6,8,12,35</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr">
+      <c r="P107" t="inlineStr">
         <is>
           <t>107</t>
         </is>
       </c>
-      <c r="Q105" t="inlineStr">
+      <c r="Q107" t="inlineStr">
         <is>
           <t>15,8,5,5,5,8,6,8,12,35</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr">
+      <c r="R107" t="inlineStr">
         <is>
           <t>hmLLLmmmlm</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr">
+      <c r="S107" t="inlineStr">
         <is>
           <t>hmLLLmmmlm</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
+      <c r="Z107" t="inlineStr">
         <is>
           <t>bfdf582e-6190-406a-b25c-eee25e104050</t>
         </is>
       </c>
-      <c r="AB105" t="inlineStr">
+      <c r="AB107" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>

--- a/sources/jack2_step8.xlsx
+++ b/sources/jack2_step8.xlsx
@@ -1139,6 +1139,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>19394d42-3833-4c2e-b3ec-46368a6b07eb</t>
+        </is>
+      </c>
       <c r="Z10" t="inlineStr">
         <is>
           <t>19394d42-3833-4c2e-b3ec-46368a6b07eb</t>
@@ -1211,6 +1216,11 @@
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
         </is>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>cb4f10b6-ee04-4947-a9bf-2a0a355cad60</t>
+        </is>
+      </c>
       <c r="Z11" t="inlineStr">
         <is>
           <t>cb4f10b6-ee04-4947-a9bf-2a0a355cad60</t>
@@ -1278,6 +1288,11 @@
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
         </is>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>70ae82e4-7899-4172-9bbc-2145108370e7</t>
+        </is>
+      </c>
       <c r="Z12" t="inlineStr">
         <is>
           <t>70ae82e4-7899-4172-9bbc-2145108370e7</t>
@@ -1348,6 +1363,11 @@
       <c r="X13" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>052a3efc-5cdf-4aa6-9af6-a58c6ed3b504</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -9348,6 +9368,11 @@
           <t>sLLmmmmmmm</t>
         </is>
       </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>cedd2a7b-61d7-42fe-9349-42a2b1503d3f</t>
+        </is>
+      </c>
       <c r="Z104" t="inlineStr">
         <is>
           <t>cedd2a7b-61d7-42fe-9349-42a2b1503d3f</t>
@@ -9395,6 +9420,11 @@
           <t>sLLmmmmmlm</t>
         </is>
       </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>46414757-6bbc-43ff-bcce-43bb3e815b75</t>
+        </is>
+      </c>
       <c r="Z105" t="inlineStr">
         <is>
           <t>46414757-6bbc-43ff-bcce-43bb3e815b75</t>
@@ -9442,6 +9472,11 @@
           <t>hmLLLmmmmm</t>
         </is>
       </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>66ed2d10-6ef0-489d-ad01-ab4680052d18</t>
+        </is>
+      </c>
       <c r="Z106" t="inlineStr">
         <is>
           <t>66ed2d10-6ef0-489d-ad01-ab4680052d18</t>
@@ -9487,6 +9522,11 @@
       <c r="S107" t="inlineStr">
         <is>
           <t>hmLLLmmmlm</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>bfdf582e-6190-406a-b25c-eee25e104050</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr">

--- a/sources/jack2_step8.xlsx
+++ b/sources/jack2_step8.xlsx
@@ -417,37 +417,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB107"/>
+  <dimension ref="A1:AC107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col hidden="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col hidden="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col hidden="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
-    <col hidden="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
-    <col hidden="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col hidden="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
-    <col hidden="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="116" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="38" customWidth="1" min="25" max="25"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col hidden="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col hidden="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col hidden="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col hidden="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col hidden="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col hidden="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col hidden="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="116" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
     <col width="38" customWidth="1" min="26" max="26"/>
     <col width="38" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="38" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -475,125 +476,130 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="U2" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="V2" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="W2" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W2" s="1" t="inlineStr">
+      <c r="X2" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X2" s="1" t="inlineStr">
+      <c r="Y2" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB2" s="1" t="inlineStr">
+      <c r="AC2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -610,62 +616,62 @@
           <t>1+3</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Hell Press</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Hell Press</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Only throws on a hit in close range, damage will be 20 on out of throw range hit. Causes Guard Break on a block.</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>d1b3696d-71d2-43d8-9da7-e3cdab4f1c24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>b654cbe7-d973-4f41-8eae-1482e6eb38ed</t>
         </is>
@@ -682,67 +688,67 @@
           <t>2+4</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Gorilla Press</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Gorilla Press</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Special Tag Throw with Gun Jack only. Gun Jack finishes with a Back Breaker. Total damage is 30.</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>41a8b8a1-0d85-436f-84c1-14401a6b24a3</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>078fd015-3852-4462-a6ff-5f5c88a8c832</t>
         </is>
@@ -759,57 +765,57 @@
           <t>qcf+1</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Pyramid Driver</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Pyramid Driver</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>221224ec-f4de-4dfc-b6e1-a8dc1de49906</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>7a6efdce-1ae7-4e4f-bd1d-0867f859eefc</t>
         </is>
@@ -826,57 +832,57 @@
           <t>qcb+2</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Back Breaker</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Back Breaker</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>27c78fac-a35a-4374-b6bd-96d5560a4fdf</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>4f86a35f-6e8e-461f-8006-a08e012a506b</t>
         </is>
@@ -893,57 +899,57 @@
           <t>db,f+1+2</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Piledriver</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Piledriver</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>4b7b8564-3edf-4c7f-8152-9b88e2f622e5</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>4ad5b5e8-3e0c-470d-bd8f-dce7ed46420e</t>
         </is>
@@ -960,57 +966,57 @@
           <t>df+2+4</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Catapult</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Catapult</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>22aef2ed-72f9-43dd-95c1-b22cf0b7256d</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>def8cdf4-43cb-4ad7-8bd6-bb18ba90840e</t>
         </is>
@@ -1027,67 +1033,67 @@
           <t>df,df+1</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Modified Catapult</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Modified Catapult</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>Modified Catapult has a faster recovery then the regular Catapult, making it possible to juggle.</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>f3574a58-5281-480a-9d00-c845537e77cf</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>4b1f0b1c-52f9-4564-b493-3770e1f3f620</t>
         </is>
@@ -1104,57 +1110,57 @@
           <t>1+3,1+2</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>– Face Buster</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Hell Press – Face Buster</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>25,10</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>19394d42-3833-4c2e-b3ec-46368a6b07eb</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>19394d42-3833-4c2e-b3ec-46368a6b07eb</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>b654cbe7-d973-4f41-8eae-1482e6eb38ed</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1178,55 +1184,60 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2+5</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>Spine Cracker</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Spine Cracker</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>cb4f10b6-ee04-4947-a9bf-2a0a355cad60</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>cb4f10b6-ee04-4947-a9bf-2a0a355cad60</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1250,55 +1261,60 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2+5</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>Swirl Torpedo</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Swirl Torpedo</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>70ae82e4-7899-4172-9bbc-2145108370e7</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>70ae82e4-7899-4172-9bbc-2145108370e7</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1322,60 +1338,65 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2+5</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>Death Shot</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Death Shot</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>052a3efc-5cdf-4aa6-9af6-a58c6ed3b504</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>052a3efc-5cdf-4aa6-9af6-a58c6ed3b504</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1407,125 +1428,130 @@
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E16" s="1" t="inlineStr">
+      <c r="F16" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F16" s="1" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G16" s="1" t="inlineStr">
+      <c r="H16" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H16" s="1" t="inlineStr">
+      <c r="I16" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I16" s="1" t="inlineStr">
+      <c r="J16" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J16" s="1" t="inlineStr">
+      <c r="K16" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K16" s="1" t="inlineStr">
+      <c r="L16" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L16" s="1" t="inlineStr">
+      <c r="M16" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M16" s="1" t="inlineStr">
+      <c r="N16" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N16" s="1" t="inlineStr">
+      <c r="O16" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O16" s="1" t="inlineStr">
+      <c r="P16" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P16" s="1" t="inlineStr">
+      <c r="Q16" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q16" s="1" t="inlineStr">
+      <c r="R16" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R16" s="1" t="inlineStr">
+      <c r="S16" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S16" s="1" t="inlineStr">
+      <c r="T16" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T16" s="1" t="inlineStr">
+      <c r="U16" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U16" s="1" t="inlineStr">
+      <c r="V16" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V16" s="1" t="inlineStr">
+      <c r="W16" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W16" s="1" t="inlineStr">
+      <c r="X16" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X16" s="1" t="inlineStr">
+      <c r="Y16" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y16" s="1" t="inlineStr">
+      <c r="Z16" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z16" s="1" t="inlineStr">
+      <c r="AA16" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA16" s="1" t="inlineStr">
+      <c r="AB16" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB16" s="1" t="inlineStr">
+      <c r="AC16" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1542,77 +1568,77 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>2fa323ed-7737-42f1-b461-cf38b273ec32</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>0c814e22-1671-4e7c-b8e8-947a4cbd4300</t>
         </is>
@@ -1629,77 +1655,77 @@
           <t>2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>5fbad8cb-ea2d-4d47-b699-750afaec7c2b</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>003e6533-d461-4701-8fa1-fd2c8fb069ae</t>
         </is>
@@ -1716,77 +1742,77 @@
           <t>3</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>fc9221d5-84f0-46a2-a16b-bc6b6609a902</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>e67aeef2-94d8-47ac-bd61-4e730f351929</t>
         </is>
@@ -1803,77 +1829,77 @@
           <t>4</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>9811fd93-92ab-4f54-9536-24a9a6cb2808</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>1fc1af5d-b603-4cdb-b4be-f534eb9ff60c</t>
         </is>
@@ -1890,77 +1916,77 @@
           <t>f+1</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>3d78d553-837c-43c4-b083-0369fe1f0061</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>74330846-e131-4965-aea7-45dc951d950c</t>
         </is>
@@ -1977,77 +2003,77 @@
           <t>f+2</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>6c13df78-ce8e-4d30-bea3-0019f5f6cc90</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>756cd993-0892-400a-bf21-8c299a5e8b01</t>
         </is>
@@ -2064,77 +2090,77 @@
           <t>f+3</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>7978ec46-1a49-4cf2-8b4a-e3f9bf8a6cc2</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>47620b35-7694-422c-88e8-ae9ba05f1c0a</t>
         </is>
@@ -2151,77 +2177,77 @@
           <t>f+4</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>27a0a511-2a5b-4d3a-b7f9-b1216c896b9d</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>1da59af2-a117-4ed6-85ff-f1167e08a059</t>
         </is>
@@ -2238,77 +2264,77 @@
           <t>d+1</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>a34949b7-c929-4be9-b009-81135450075b</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>7a3e6305-3cd6-412b-aa74-0322709d2880</t>
         </is>
@@ -2325,77 +2351,77 @@
           <t>d+2</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>fd0862a5-8315-4cb8-9f1f-893a42386e32</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>a4d5c5e9-217f-481e-8670-72ed0d9a4ecb</t>
         </is>
@@ -2412,77 +2438,77 @@
           <t>d+3</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>680e062c-9470-4e46-adbd-8f9b1b295a80</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>3fe49bc1-1a18-4473-9b72-583f91f7a8df</t>
         </is>
@@ -2499,77 +2525,77 @@
           <t>d+4</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>d4e74cde-9624-4a9b-a5c4-1bde693fa77b</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>5b1b776a-dd90-4a98-9b3a-3c9a3f93e10e</t>
         </is>
@@ -2586,77 +2612,77 @@
           <t>FC+1</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>1dc624f3-e83b-4410-9a14-e55d03089928</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>d8a72cb4-1fb6-4c37-bbf1-570b518e9b47</t>
         </is>
@@ -2673,77 +2699,77 @@
           <t>FC+2</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>5d80f6c9-bc23-46e1-8303-5d5e1192105f</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>18254d49-42dc-4447-83d3-2f91f81a5ee7</t>
         </is>
@@ -2760,77 +2786,77 @@
           <t>FC+3</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>795dbef8-f107-4f0d-890f-83cf62ecefcc</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>c9a2965b-2fd6-4f02-b793-0f2b17b835d8</t>
         </is>
@@ -2847,77 +2873,77 @@
           <t>FC+4</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>aa390085-4302-45e6-bad6-1c6ab70220d5</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>661e188a-22fe-40c3-af9d-7990d5dbfe02</t>
         </is>
@@ -2934,77 +2960,77 @@
           <t>WS+1</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>7a4e95bc-37b7-41df-82a0-0915a44b1110</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>ef6993da-e049-427e-bcc8-cb4b4c1dd8b1</t>
         </is>
@@ -3021,77 +3047,77 @@
           <t>WS+2</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>165e0eb2-296c-45a9-807c-afdfa8c58e8d</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>b7ce6ad6-cd2f-4c1a-8b20-d9d6cd143f82</t>
         </is>
@@ -3108,77 +3134,77 @@
           <t>WS+3</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>52e1b2fb-3de9-4a53-ad06-346b3df48952</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>1979672c-a730-43e4-962d-dd5adb17a3c2</t>
         </is>
@@ -3195,77 +3221,77 @@
           <t>WS+4</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>6d241305-ebd1-49bc-a46d-58a3b875a6d1</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>63048d8d-b8e8-49ec-bfa1-3e70f47c6e4d</t>
         </is>
@@ -3282,77 +3308,77 @@
           <t>df+1</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>b2fa0fc5-05fd-42a2-b25f-186c0abe34a8</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>9042603c-662b-4207-96ad-276188c2aea0</t>
         </is>
@@ -3369,77 +3395,77 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>840e562a-5d3a-4245-a7c9-aac9df654f01</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>e6493757-0145-4cd8-9118-2a98dae2e246</t>
         </is>
@@ -3456,77 +3482,77 @@
           <t>df+3</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>70e7e712-844c-462b-945f-53b90dfdb65e</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>d1056fa8-9a11-4916-a1b6-a971f4b3fb23</t>
         </is>
@@ -3543,77 +3569,77 @@
           <t>df+4</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>d023a5fc-29f2-4a72-84cf-ed164225f361</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>fba1e3ea-1796-4aa1-94f4-3e23f3fcc1fb</t>
         </is>
@@ -3645,125 +3671,130 @@
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E43" s="1" t="inlineStr">
+      <c r="F43" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F43" s="1" t="inlineStr">
+      <c r="G43" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G43" s="1" t="inlineStr">
+      <c r="H43" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H43" s="1" t="inlineStr">
+      <c r="I43" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I43" s="1" t="inlineStr">
+      <c r="J43" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J43" s="1" t="inlineStr">
+      <c r="K43" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K43" s="1" t="inlineStr">
+      <c r="L43" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L43" s="1" t="inlineStr">
+      <c r="M43" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M43" s="1" t="inlineStr">
+      <c r="N43" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N43" s="1" t="inlineStr">
+      <c r="O43" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O43" s="1" t="inlineStr">
+      <c r="P43" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P43" s="1" t="inlineStr">
+      <c r="Q43" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q43" s="1" t="inlineStr">
+      <c r="R43" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R43" s="1" t="inlineStr">
+      <c r="S43" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S43" s="1" t="inlineStr">
+      <c r="T43" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T43" s="1" t="inlineStr">
+      <c r="U43" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U43" s="1" t="inlineStr">
+      <c r="V43" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V43" s="1" t="inlineStr">
+      <c r="W43" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W43" s="1" t="inlineStr">
+      <c r="X43" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X43" s="1" t="inlineStr">
+      <c r="Y43" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y43" s="1" t="inlineStr">
+      <c r="Z43" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z43" s="1" t="inlineStr">
+      <c r="AA43" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA43" s="1" t="inlineStr">
+      <c r="AB43" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB43" s="1" t="inlineStr">
+      <c r="AC43" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3780,87 +3811,87 @@
           <t>1,1,1</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Jack Hammer</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Jack Hammer</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>-7 -9 -13</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>-7 -9 -13</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>+4 0 KD</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>+4 0 KD</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>+4 0 KD</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>+4 0 KD</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>18,15,18</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>18,15,18</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>0223c57b-a823-44fe-83a4-bc74507b234e</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>266c911e-d99f-4b3d-a759-b73fc533073d</t>
         </is>
@@ -3877,97 +3908,97 @@
           <t>WS+1</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Violent Uppercut</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Violent Uppercut</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>83ebb1e0-70d0-49c8-b147-3404721fc0e1</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>ef006b10-18dd-421c-94db-6ccaceb6a133</t>
         </is>
@@ -3984,82 +4015,82 @@
           <t>db+1,1,1,2</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Machine Gun - Megaton Punch</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Machine Gun - Megaton Punch</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>-6 -6 -11 -16</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>-6 -6 -11 -16</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>+5 +5 0 KD</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>+5 +5 0 KD</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>+5 +5 0 KD</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>+5 +5 0 KD</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>12,15,15,40</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>12,15,15,40</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>lllm</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>lllm</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>dc5a29f5-7ecb-4a43-967e-7b5eadf20512</t>
         </is>
@@ -4076,82 +4107,82 @@
           <t>db+1,1,1,1,2</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Machine Gun - Megaton Punch</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Machine Gun - Megaton Punch</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>-6 -6 -6 -11 -16</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>-6 -6 -6 -11 -16</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>+5 +5 +5 0 KD</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>+5 +5 +5 0 KD</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>+5 +5 +5 0 KD</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>+5 +5 +5 0 KD</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>12,15,15,15,40</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>12,15,15,15,40</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>llllm</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>llllm</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>b3cad2bc-95a3-4d7c-9abb-0335ed57fb7d</t>
         </is>
@@ -4168,82 +4199,82 @@
           <t>db+1,1,1,1,1,2</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Machine Gun - Megaton Punch</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Machine Gun - Megaton Punch</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>-6 -6 -6 -6 -11 -16</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>-6 -6 -6 -6 -11 -16</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>+5 +5 +5 +5 0 KD</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>+5 +5 +5 +5 0 KD</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>+5 +5 +5 +5 0 KD</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>+5 +5 +5 +5 0 KD</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>12,15,15,15,15,40</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>12,15,15,15,15,40</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>lllllm</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>lllllm</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>3a6ce42c-3b05-4641-9152-428a8ed9fd0f</t>
         </is>
@@ -4260,92 +4291,92 @@
           <t>b,db,d,DF+1</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Debugger</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Debugger</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>-45</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>-45</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>85158165-351f-41d2-8735-2ab0b63af148</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>2747e1e2-0cb3-4730-81ad-dc7a7427a2b6</t>
         </is>
@@ -4369,45 +4400,50 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>b,b+1</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>Wind Up</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Wind Up</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>c03fb65b-aaac-4006-8e2b-0a9f8c08fd8f</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="AA50" t="inlineStr">
         <is>
           <t>1a0aed99-b547-48d7-925a-8f99bbeb0917</t>
         </is>
@@ -4424,92 +4460,92 @@
           <t>hcf,1</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Gigaton Punch</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Wind Up – Gigaton Punch</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>+21</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>+21</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>-,20</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>-m</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>2003590c-d918-44b9-ba39-ae204bd6ae62</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>4b654016-9d3d-4588-aaf3-bcba06d600eb</t>
         </is>
       </c>
-      <c r="AA51" t="inlineStr">
+      <c r="AB51" t="inlineStr">
         <is>
           <t>c03fb65b-aaac-4006-8e2b-0a9f8c08fd8f</t>
         </is>
@@ -4526,92 +4562,92 @@
           <t>hcf,DF+1</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Debugger</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Wind Up – Debugger</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>-45</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>-45</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>-,25</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>-L</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>bfcd8070-9fe9-4f68-b19e-bddec360b30a</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>bc7743df-d62c-4baf-90d6-ca367a954aba</t>
         </is>
       </c>
-      <c r="AA52" t="inlineStr">
+      <c r="AB52" t="inlineStr">
         <is>
           <t>c03fb65b-aaac-4006-8e2b-0a9f8c08fd8f</t>
         </is>
@@ -4628,97 +4664,97 @@
           <t>DF+1,2,1,2</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Uppercut Rush</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Uppercut Rush</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>-11 -7 -9 -2</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>-11 -7 -9 -2</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>KD +4 +2 +9</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>KD +4 +2 +9</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>KD +4 +2 +9</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>KD +4 +2 +9</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>10,15,10,15</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>10,15,10,15</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>mmmm</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>mmmm</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>JGc RC</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>Juggles on the last hit if the first hit was a counter hit.</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>4f881878-519e-4f9f-bb13-ebe8511b7e9f</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>bf72dea8-4c41-4bb6-9420-9305240a53e3</t>
         </is>
@@ -4727,12 +4763,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Df+1,2,1</t>
+          <t>DF,1,2,1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Df+1,2,1</t>
+          <t>DF,1,2,1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4742,95 +4778,100 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>FC+DF+1,2,1</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>Quick Upper Rush</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Quick Upper Rush</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>-6 -8 -2</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>-6 -8 -2</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>+5 +2 +9</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>+5 +2 +9</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>+5 +2 +9</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>+5 +2 +9</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>15,12,15</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>15,12,15</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>JGc RC</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>Juggles on the last hit if the first hit was a counter hit.</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>7507a693-7948-45eb-a05e-3707d923e16d</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>b30faab6-54e4-4123-ab0b-5fb12faa3be2</t>
         </is>
@@ -4847,87 +4888,87 @@
           <t>FC+df+1,2,1</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Windmill</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Windmill</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>-22 -22 -2</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>-22 -22 -2</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>-12 -12 -12</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>-12 -12 -12</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>-12 -12 -12</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>-12 -12 -12</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>10,15,10</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>10,15,10</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>dbb96ec3-9f0f-4e57-b4ca-8de7e5046661</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
+      <c r="AA55" t="inlineStr">
         <is>
           <t>1c7f46c4-6ab3-4fdd-90e3-5f642409d3af</t>
         </is>
@@ -4944,92 +4985,92 @@
           <t>FC+df+1,2,1,1</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>– Windmill Backhand</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Windmill – Windmill Backhand</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>+20</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>-22 -22 -2 +20</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>-12 -12 -12 KD</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>-12 -12 -12 KD</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>10,15,10,30</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>mmmh</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
+      <c r="W56" t="inlineStr">
         <is>
           <t>CF GB</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>82838a4d-d558-42b7-ab73-e05d17ef4b08</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>e3e5f6b7-4929-4a52-8c31-e6806f1334ee</t>
         </is>
       </c>
-      <c r="AA56" t="inlineStr">
+      <c r="AB56" t="inlineStr">
         <is>
           <t>dbb96ec3-9f0f-4e57-b4ca-8de7e5046661</t>
         </is>
@@ -5038,12 +5079,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Df+1,2</t>
+          <t>DF,1,2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Df+1,2</t>
+          <t>DF,1,2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5053,90 +5094,95 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>FC+DF+1,2</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>Medium Hammer Rush</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Medium Hammer Rush</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>-6 -8</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>-6 -8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>+5 +2</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>+5 +2</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>+5 +2</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>+5 +2</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>15,12</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>15,12</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="W57" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
+      <c r="AA57" t="inlineStr">
         <is>
           <t>53b77124-e72d-4f20-ae78-8225f04ac648</t>
         </is>
@@ -5150,95 +5196,95 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Df+1,2,d+1</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
+          <t>DF,1,2,d+1</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
         <is>
           <t>– Low Punch</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Medium Hammer Rush – Low Punch</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>-6 -8 -17</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>+5 +2 -7</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>+5 +2 -7</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>15,12,8</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>mmL</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>29dfa2dc-0160-4e71-b110-03e973136272</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
+      <c r="AA58" t="inlineStr">
         <is>
           <t>be700e61-7fed-40b2-a16a-4b062cedd1c9</t>
         </is>
       </c>
-      <c r="AA58" t="inlineStr">
+      <c r="AB58" t="inlineStr">
         <is>
           <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
         </is>
@@ -5252,95 +5298,95 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Df+1,2,df+1</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
+          <t>DF,1,2,df+1</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
         <is>
           <t>– Mid Punch</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Medium Hammer Rush – Mid Punch</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>-6 -8 -1</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>+5 +2 +10</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>+5 +2 +10</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>15,12,15</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>eb9bbfe4-68c3-4e58-baf7-821687138e91</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
+      <c r="AA59" t="inlineStr">
         <is>
           <t>636b5aa8-46de-464e-81e9-d0bcfa43dc73</t>
         </is>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AB59" t="inlineStr">
         <is>
           <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
         </is>
@@ -5354,90 +5400,90 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Df+1,2,f+1</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
+          <t>DF,1,2,f+1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
         <is>
           <t>– High Punch</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Medium Hammer Rush – High Punch</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>-6 -8 -17</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>+5 +2 -5</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>+5 +2 -5</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>15,12,12</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>mmh</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>897a7dd1-1093-48ff-85f1-bebca88601ea</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>96ffff19-8555-4463-82fe-458f7c0c053b</t>
         </is>
       </c>
-      <c r="AA60" t="inlineStr">
+      <c r="AB60" t="inlineStr">
         <is>
           <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
         </is>
@@ -5454,92 +5500,92 @@
           <t>FC+1,1,1,2</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Hammer Rush</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Hammer Rush</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>-8 +1 -12 -8</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>-8 +1 -12 -8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>+2 +12 -1 +1</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>+2 +12 -1 +1</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>+2 +12 -1 +1</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>+2 +12 -1 +1</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>10,8,12,12</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>10,8,12,12</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>LLmm</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>LLmm</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>87b157c8-bac6-4b55-a543-03b3e5c1c00f</t>
         </is>
@@ -5556,92 +5602,92 @@
           <t>FC+1,1,1,2,d+1</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>– Low Punch</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Hammer Rush – Low Punch</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>-8 +1 -12 -8 -17</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>+2 +12 -1 +1 -7</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>+2 +12 -1 +1 -7</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>10,8,12,12,8</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>LLmmL</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>acb95787-cedc-4b5b-b8fb-50a3e72d4b5b</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>19e50734-0a3e-439a-bb45-d0541eae3da2</t>
         </is>
       </c>
-      <c r="AA62" t="inlineStr">
+      <c r="AB62" t="inlineStr">
         <is>
           <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
         </is>
@@ -5658,92 +5704,92 @@
           <t>FC+1,1,1,2,df+1</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>– Mid Punch</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Hammer Rush – Mid Punch</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>-8 +1 -12 -8 -1</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>+2 +12 -1 +1 +10</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>+2 +12 -1 +1 +10</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>10,8,12,12,15</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>LLmmm</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr">
+      <c r="W63" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>756e1d64-081b-4d25-aaa0-fa5c3b7a738f</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>ecd60ebe-4c07-4ca2-a44b-3748905360dd</t>
         </is>
       </c>
-      <c r="AA63" t="inlineStr">
+      <c r="AB63" t="inlineStr">
         <is>
           <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
         </is>
@@ -5760,87 +5806,87 @@
           <t>FC+1,1,1,2,f+1</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>– High Punch</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Hammer Rush – High Punch</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>-8 +1 -12 -8 -17</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>+2 +12 -1 +1 -5</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>+2 +12 -1 +1 -5</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>10,8,12,12,12</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>LLmmh</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>ac1b3ebe-7028-47a0-be65-5eb121dab8bc</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>fe5b804b-6426-463e-b283-4eb22f9998b3</t>
         </is>
       </c>
-      <c r="AA64" t="inlineStr">
+      <c r="AB64" t="inlineStr">
         <is>
           <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
         </is>
@@ -5857,92 +5903,92 @@
           <t>FC+1,2</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>Low Punch - Megaton Punch</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Low Punch - Megaton Punch</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>-8 -14</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>-8 -14</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>+2 KD</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>+2 KD</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>+2 KD</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>+2 KD</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>10,25</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>10,25</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>Lm</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>Lm</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr">
+      <c r="W65" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>06ab7954-5d39-49cc-91e3-02c54893dd53</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>a769fb07-8a59-436e-a5fb-3acd34e8e01d</t>
         </is>
@@ -5959,97 +6005,97 @@
           <t>SS+1</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Jack Hammer</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Jack Hammer</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr">
+      <c r="W66" t="inlineStr">
         <is>
           <t>BN GB</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>41456c1a-f3a2-468f-b0ee-ee2032bb78c8</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
+      <c r="AA66" t="inlineStr">
         <is>
           <t>de86a0e0-55fd-41e5-a239-a7685c39edbd</t>
         </is>
@@ -6066,87 +6112,87 @@
           <t>SS+1+2</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Double Knuckle Swing</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Double Knuckle Swing</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>15c368e0-8f76-42a0-bbea-ef3cc510e19c</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>2f8a7e04-7a60-430d-bc0a-6a55ed0d3427</t>
         </is>
@@ -6163,92 +6209,92 @@
           <t>1+2&lt;1+2</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>Hammer Knuckle - Double Uppercut</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Hammer Knuckle - Double Uppercut</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>-15 -20</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>-15 -20</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>21,22</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>21,22</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr">
+      <c r="W68" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>54667fc1-c443-4001-a9d7-46c1d391bc4d</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>36af744c-98c3-48c0-bea9-c96c61093c26</t>
         </is>
@@ -6265,92 +6311,92 @@
           <t>WS+1+2&lt;1+2</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>Double Uppercut - Hammer Knuckle</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Double Uppercut - Hammer Knuckle</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>-15 -16</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>-15 -16</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>21,17</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="R69" t="inlineStr">
         <is>
           <t>21,17</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr">
+      <c r="W69" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>14470b5f-e125-4262-857b-20fa6db24ee3</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
+      <c r="AA69" t="inlineStr">
         <is>
           <t>45985eea-a458-447f-9b9d-941ed088446a</t>
         </is>
@@ -6367,92 +6413,92 @@
           <t>f+1+2</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>Arm Scissors</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Arm Scissors</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr">
+      <c r="W70" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
+      <c r="AA70" t="inlineStr">
         <is>
           <t>f51b4cde-994c-422f-b3e6-3e932f7d87ff</t>
         </is>
@@ -6469,92 +6515,92 @@
           <t>f+1+2,1+2</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>– Cross Cut Saw</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Arm Scissors – Cross Cut Saw</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>-10 -14</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="R71" t="inlineStr">
         <is>
           <t>17,15</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>ml</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr">
+      <c r="W71" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>acab70ca-8813-48c6-907e-58ba82b57685</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
+      <c r="AA71" t="inlineStr">
         <is>
           <t>e7af4cd0-902b-4b89-9c43-ea9365bec42c</t>
         </is>
       </c>
-      <c r="AA71" t="inlineStr">
+      <c r="AB71" t="inlineStr">
         <is>
           <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
         </is>
@@ -6571,92 +6617,92 @@
           <t>f+1+2~df+2</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>– Megaton Punch</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Arm Scissors – Megaton Punch</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>-10 -19</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="R72" t="inlineStr">
         <is>
           <t>17,25</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="T72" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="V72" t="inlineStr">
+      <c r="W72" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t>773af138-28f0-48ff-9b0e-97e83d2d8d3f</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
+      <c r="AA72" t="inlineStr">
         <is>
           <t>b671f9fe-a460-4157-8300-00379e99322d</t>
         </is>
       </c>
-      <c r="AA72" t="inlineStr">
+      <c r="AB72" t="inlineStr">
         <is>
           <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
         </is>
@@ -6673,102 +6719,102 @@
           <t>d+1+2</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>Bravo Knuckle</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Bravo Knuckle</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>-23</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>-23</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="R73" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="T73" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V73" t="inlineStr">
+      <c r="W73" t="inlineStr">
         <is>
           <t>JG GB</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>When tagging in Bryan Fury hit 2 to grab the opponent in mid air and do a Fisherman's Slam. Total damage is 21,21.</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
+      <c r="Y73" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>f79bf7d8-dcd1-4a58-883f-38e113a7b9e1</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
+      <c r="AA73" t="inlineStr">
         <is>
           <t>2ecc5ad9-b4ca-485a-884a-0301a91b3509</t>
         </is>
@@ -6785,92 +6831,92 @@
           <t>FC+1+2</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>Cross Cut Saw</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Cross Cut Saw</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="R74" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="T74" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="V74" t="inlineStr">
+      <c r="W74" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t>23e71f4e-0ab8-4ddc-89c1-4b2fe81234cc</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
+      <c r="AA74" t="inlineStr">
         <is>
           <t>52606470-ef56-4c68-a311-9fe12c9a5f23</t>
         </is>
@@ -6879,12 +6925,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Df+2,1,2</t>
+          <t>DF,2,1,2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Df+2,1,2</t>
+          <t>DF,2,1,2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6894,95 +6940,100 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t>FC+DF+2,1,2</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>Quick Uppercut Rush</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Quick Uppercut Rush</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>-9 -2 -9</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>-9 -2 -9</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>-2 +10 +2</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>-2 +10 +2</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>-2 +10 +2</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>-2 +10 +2</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>15,10,15</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="R75" t="inlineStr">
         <is>
           <t>15,10,15</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="V75" t="inlineStr">
+      <c r="W75" t="inlineStr">
         <is>
           <t>JGc RC</t>
         </is>
       </c>
-      <c r="W75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>Juggles on the last hit if the first hit was a counter hit.</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t>38964142-4e38-457c-9a6d-9ef0fcf12cd4</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
+      <c r="AA75" t="inlineStr">
         <is>
           <t>8efe400a-6435-45e4-92f5-b9e1d4fd9595</t>
         </is>
@@ -6999,92 +7050,92 @@
           <t>DF+2,1,2,1</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>Hammer Uppercut Rush</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Hammer Uppercut Rush</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>-11 -6 -9 -1</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>-11 -6 -9 -1</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>KD +5 +3 +10</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>KD +5 +3 +10</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>KD +5 +3 +10</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>KD +5 +3 +10</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>10,15,12,15</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="R76" t="inlineStr">
         <is>
           <t>10,15,12,15</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>mmmm</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t>mmmm</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr">
+      <c r="W76" t="inlineStr">
         <is>
           <t>JG RC</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>f62fd939-223c-47b4-982b-aecff23cfca4</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
+      <c r="AA76" t="inlineStr">
         <is>
           <t>e85a400e-73a4-495b-917a-82244da3681f</t>
         </is>
@@ -7101,87 +7152,87 @@
           <t>f,f+2</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>Atomic Hook</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Atomic Hook</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="R77" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="T77" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>e3ef4e95-cdea-4525-83df-74474e814b2a</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
+      <c r="AA77" t="inlineStr">
         <is>
           <t>e14fe285-946c-414b-88e4-d7e2f3af2745</t>
         </is>
@@ -7198,97 +7249,97 @@
           <t>2,1,2</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>Punch - Elbow - Uppercut</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>Punch - Elbow - Uppercut</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>0 0 -15</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>0 0 -15</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>+7 +2 KD</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>+7 +2 KD</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>+7 +2 KD</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>+7 +2 KD</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>12,15,20</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="R78" t="inlineStr">
         <is>
           <t>12,15,20</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr">
+      <c r="S78" t="inlineStr">
         <is>
           <t>hmm</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="T78" t="inlineStr">
         <is>
           <t>hmm</t>
         </is>
       </c>
-      <c r="V78" t="inlineStr">
+      <c r="W78" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
+      <c r="Y78" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr">
+      <c r="Z78" t="inlineStr">
         <is>
           <t>b51b9f18-a0d7-4234-b6c4-e0db8e729094</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
+      <c r="AA78" t="inlineStr">
         <is>
           <t>06e4e99f-b024-4491-a080-43e24bdee8bc</t>
         </is>
@@ -7297,12 +7348,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Df+2</t>
+          <t>DF,2</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Df+2</t>
+          <t>DF,2</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -7312,90 +7363,95 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t>FC+df+2</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
           <t>Short Hammer Rush</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Short Hammer Rush</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="R79" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="T79" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V79" t="inlineStr">
+      <c r="W79" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr">
+      <c r="Z79" t="inlineStr">
         <is>
           <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
+      <c r="AA79" t="inlineStr">
         <is>
           <t>d79c3cf7-3a6f-4c0a-b31a-e35de47e6878</t>
         </is>
@@ -7409,95 +7465,95 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Df+2,d+1</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
+          <t>DF,2,d+1</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
         <is>
           <t>– Low Punch</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Short Hammer Rush – Low Punch</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>-13 -17</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>-2 -7</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>-2 -7</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
+      <c r="R80" t="inlineStr">
         <is>
           <t>10,8</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="T80" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="V80" t="inlineStr">
+      <c r="W80" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr">
+      <c r="Z80" t="inlineStr">
         <is>
           <t>82744639-21bd-464e-acb0-fb430a833b71</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
+      <c r="AA80" t="inlineStr">
         <is>
           <t>da44dd7b-4cdb-4823-a817-06318a68273c</t>
         </is>
       </c>
-      <c r="AA80" t="inlineStr">
+      <c r="AB80" t="inlineStr">
         <is>
           <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
         </is>
@@ -7511,95 +7567,95 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Df+2,df+1</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
+          <t>DF,2,df+1</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
         <is>
           <t>– Mid Punch</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Short Hammer Rush – Mid Punch</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>-13 -1</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>-2 +10</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>+10</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>-2 +10</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="R81" t="inlineStr">
         <is>
           <t>10,15</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="T81" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="V81" t="inlineStr">
+      <c r="W81" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
+      <c r="Z81" t="inlineStr">
         <is>
           <t>9cba188e-9985-4f96-83e4-7db5474781d2</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
+      <c r="AA81" t="inlineStr">
         <is>
           <t>51f0fb87-39b1-45cd-ab41-c081312a5d9b</t>
         </is>
       </c>
-      <c r="AA81" t="inlineStr">
+      <c r="AB81" t="inlineStr">
         <is>
           <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
         </is>
@@ -7613,90 +7669,90 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Df+2,f+1</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
+          <t>DF,2,f+1</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
         <is>
           <t>– High Punch</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Short Hammer Rush – High Punch</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>-13 -17</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>-2 -5</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>-2 -5</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="R82" t="inlineStr">
         <is>
           <t>10,12</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="T82" t="inlineStr">
         <is>
           <t>mh</t>
         </is>
       </c>
-      <c r="Y82" t="inlineStr">
+      <c r="Z82" t="inlineStr">
         <is>
           <t>9dd1c03f-e1e1-4e41-b91a-88df8054ec5c</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
+      <c r="AA82" t="inlineStr">
         <is>
           <t>529ea903-bd1d-4081-ab74-eb6b82eaab94</t>
         </is>
       </c>
-      <c r="AA82" t="inlineStr">
+      <c r="AB82" t="inlineStr">
         <is>
           <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
         </is>
@@ -7713,92 +7769,92 @@
           <t>b,db,d,DF+2</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>Megaton Punch</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Megaton Punch</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr">
+      <c r="P83" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="R83" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
+      <c r="T83" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V83" t="inlineStr">
+      <c r="W83" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y83" t="inlineStr">
+      <c r="Z83" t="inlineStr">
         <is>
           <t>56b1623c-ef98-42a3-be49-2ebc46462a0f</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
+      <c r="AA83" t="inlineStr">
         <is>
           <t>e818b2a1-12e3-409b-8e48-4b059aaa76c0</t>
         </is>
@@ -7815,87 +7871,87 @@
           <t>f,f+3</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>Granite Stomp</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Granite Stomp</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
+      <c r="P84" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
+      <c r="R84" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="S84" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
+      <c r="T84" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
+      <c r="Z84" t="inlineStr">
         <is>
           <t>ee6c0589-29fe-439a-8f69-242d8e6811f6</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
+      <c r="AA84" t="inlineStr">
         <is>
           <t>879d1a1f-95b2-4081-aa4b-dc74da0c13c6</t>
         </is>
@@ -7919,85 +7975,90 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t>FC+df+3+4</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>Giga Shoulder Ram</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Giga Shoulder Ram</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr">
+      <c r="P85" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr">
+      <c r="R85" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
+      <c r="T85" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
+      <c r="Z85" t="inlineStr">
         <is>
           <t>20d7633a-2326-4494-84f9-0a235f1c2fe8</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
+      <c r="AA85" t="inlineStr">
         <is>
           <t>b0da65f9-bf50-406e-8de8-7db02d0abb2c</t>
         </is>
@@ -8014,87 +8075,87 @@
           <t>DB+3,4,3,4,3,4</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>Cossack Kicks</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Cossack Kicks</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>-20 -22 -20 -22...</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t>-20 -22 -20 -22...</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>-9 -11 -9 -11...</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>-9 -11 -9 -11...</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>-9 -11 -9 -11...</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>-9 -11 -9 -11...</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
+      <c r="P86" t="inlineStr">
         <is>
           <t>18,12,10,12,12,12</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
+      <c r="Q86" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr">
+      <c r="R86" t="inlineStr">
         <is>
           <t>18,12,10,12,12,12</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr">
+      <c r="S86" t="inlineStr">
         <is>
           <t>LLLLLL</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
+      <c r="T86" t="inlineStr">
         <is>
           <t>LLLLLL</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
+      <c r="Z86" t="inlineStr">
         <is>
           <t>674f6841-5fbb-4b15-865f-9ab351c1a0f0</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
+      <c r="AA86" t="inlineStr">
         <is>
           <t>4c477a6b-86e6-43f8-911d-93481004b0b5</t>
         </is>
@@ -8111,92 +8172,92 @@
           <t>uf+3+4</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>Hip Press</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>Hip Press</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>-40</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>-40</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t>-40</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
+      <c r="O87" t="inlineStr">
         <is>
           <t>-40</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr">
+      <c r="P87" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
+      <c r="Q87" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr">
+      <c r="R87" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr">
+      <c r="S87" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
+      <c r="T87" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="W87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>If the Hip Press Misses the opponent, Jack-2 can chain into Sit Down extentions.</t>
         </is>
       </c>
-      <c r="Y87" t="inlineStr">
+      <c r="Z87" t="inlineStr">
         <is>
           <t>3be14565-e783-4db3-9168-bf98e290f21d</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
+      <c r="AA87" t="inlineStr">
         <is>
           <t>ce4da910-2232-4be6-a896-136d900764e1</t>
         </is>
@@ -8213,149 +8274,151 @@
           <t>3+4</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>Sit Down</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Sit Down</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr">
+      <c r="P88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
+      <c r="Q88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr">
+      <c r="R88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr">
+      <c r="S88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
+      <c r="T88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y88" t="inlineStr">
+      <c r="Z88" t="inlineStr">
         <is>
           <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
+      <c r="AA88" t="inlineStr">
         <is>
           <t>8ff726df-3bc4-4645-98be-c2fad557ee7d</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89">
-        <f>~3+4</f>
-        <v/>
-      </c>
-      <c r="B89">
-        <f>~3+4</f>
-        <v/>
-      </c>
-      <c r="D89" t="inlineStr">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>– ~3+4</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>3+4~3+4</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
         <is>
           <t>– Hop Hip Press</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>– Hop Hip Press</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Sit Down – Hop Hip Press</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>-34</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>-34</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t>-34</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
+      <c r="O89" t="inlineStr">
         <is>
           <t>-34</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr">
+      <c r="P89" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
+      <c r="Q89" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="R89" t="inlineStr">
         <is>
+          <t>-,35</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
           <t>M</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>-M</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
         <is>
           <t>If the Hip Press Misses the opponent, Jack-2 can chain into Sit Down extentions.</t>
         </is>
       </c>
-      <c r="Y89" t="inlineStr">
+      <c r="Z89" t="inlineStr">
         <is>
           <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
+      <c r="AA89" t="inlineStr">
         <is>
           <t>1f37a24d-750f-4851-a2b5-a6b9a1b4ed26</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
@@ -8365,78 +8428,59 @@
           <t>– B</t>
         </is>
       </c>
-      <c r="B90">
-        <f>~3+4,B</f>
-        <v/>
-      </c>
-      <c r="D90" t="inlineStr">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>3+4,B</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
         <is>
           <t>– Roll Back</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>– Hop Hip Press – Roll Back</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>-34</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>-34</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr">
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Sit Down – Roll Back</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
+      <c r="Q90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>35,-</t>
-        </is>
-      </c>
       <c r="R90" t="inlineStr">
         <is>
+          <t>-,-</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
         <is>
           <t>a96a391b-b0cf-493d-a205-6511f1e34903</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
+      <c r="AA90" t="inlineStr">
         <is>
           <t>4f15e677-cb84-4d03-b6d8-82c26255c1d9</t>
         </is>
       </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
@@ -8446,78 +8490,59 @@
           <t>– F</t>
         </is>
       </c>
-      <c r="B91">
-        <f>~3+4,F</f>
-        <v/>
-      </c>
-      <c r="D91" t="inlineStr">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>3+4,F</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
         <is>
           <t>– Roll Forward</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>– Hop Hip Press – Roll Forward</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>-34</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>-34</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr">
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Sit Down – Roll Forward</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="Q91" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>35,-</t>
-        </is>
-      </c>
       <c r="R91" t="inlineStr">
         <is>
+          <t>-,-</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
         <is>
           <t>df8e44d6-d84c-4ee6-8117-15cb0b65ceb6</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
+      <c r="AA91" t="inlineStr">
         <is>
           <t>0680a704-d8c9-47e5-91a9-98babe1c15af</t>
         </is>
       </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
@@ -8527,50 +8552,51 @@
           <t>– 1,2,1,2</t>
         </is>
       </c>
-      <c r="B92">
-        <f>~3+4,1,2,1,2</f>
-        <v/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>3+4,1,2,1,2</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
+        </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t>3+4,2,1,2,1</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
           <t>– Sitting Punches</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>– Hop Hip Press – Sitting Punches</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Sit Down – Sitting Punches</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>-45 -43 -45 -43</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>+3 -45 -43 -45 -43</t>
-        </is>
-      </c>
       <c r="K92" t="inlineStr">
         <is>
+          <t>-45 -43 -45 -43</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
           <t>-35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>-34 -35 -32 -35 -32</t>
-        </is>
-      </c>
       <c r="M92" t="inlineStr">
         <is>
           <t>-35 -32 -35 -32</t>
@@ -8578,47 +8604,52 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>-34 -35 -32 -35 -32</t>
+          <t>-35 -32 -35 -32</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
+          <t>-35 -32 -35 -32</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
           <t>10,10,10,10</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
+      <c r="Q92" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>35,10,10,10,10</t>
-        </is>
-      </c>
       <c r="R92" t="inlineStr">
         <is>
+          <t>-,10,10,10,10</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
           <t>llll</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>Mllll</t>
-        </is>
-      </c>
-      <c r="Y92" t="inlineStr">
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>-llll</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
         <is>
           <t>1e575213-1523-40b8-9492-0a92235d1799</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
+      <c r="AA92" t="inlineStr">
         <is>
           <t>71c8d35f-24b6-430d-abc5-2ff4c47a8f3b</t>
         </is>
       </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
@@ -8633,77 +8664,77 @@
           <t>KND d+1+2</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>Spring Hammer - Sit Down</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>Spring Hammer - Sit Down</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>+20</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t>+20</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>+14</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>+14</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="N93" t="inlineStr">
         <is>
           <t>+14</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr">
+      <c r="O93" t="inlineStr">
         <is>
           <t>+14</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr">
+      <c r="P93" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr">
+      <c r="Q93" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr">
+      <c r="R93" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr">
+      <c r="S93" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr">
+      <c r="T93" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y93" t="inlineStr">
+      <c r="Z93" t="inlineStr">
         <is>
           <t>9ea7e1a3-859f-438a-b3fc-0ff0de0e315f</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
+      <c r="AA93" t="inlineStr">
         <is>
           <t>0066d9e6-44cc-4c22-b95a-1c01b1cb1dcb</t>
         </is>
@@ -8720,87 +8751,97 @@
           <t>KND d+1+2,1,2,1,2</t>
         </is>
       </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
+        </is>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t>KND d+1+2,2,1,2,1</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>– Sitting Punches</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>Spring Hammer - Sit Down – Sitting Punches</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>-45 -43 -45 -43</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="K94" t="inlineStr">
         <is>
           <t>+20 -45 -43 -45 -43</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t>-35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t>+14 -35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr">
+      <c r="N94" t="inlineStr">
         <is>
           <t>-35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
+      <c r="O94" t="inlineStr">
         <is>
           <t>+14 -35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr">
+      <c r="P94" t="inlineStr">
         <is>
           <t>10,10,10,10</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr">
+      <c r="Q94" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q94" t="inlineStr">
+      <c r="R94" t="inlineStr">
         <is>
           <t>12,10,10,10,10</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr">
+      <c r="S94" t="inlineStr">
         <is>
           <t>llll</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr">
+      <c r="T94" t="inlineStr">
         <is>
           <t>mllll</t>
         </is>
       </c>
-      <c r="Y94" t="inlineStr">
+      <c r="Z94" t="inlineStr">
         <is>
           <t>eb0c424e-d4b0-438e-bfb7-164bbca1894a</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
+      <c r="AA94" t="inlineStr">
         <is>
           <t>01e88eb2-b793-4ba3-9d87-7f7b3ab33381</t>
         </is>
       </c>
-      <c r="AA94" t="inlineStr">
+      <c r="AB94" t="inlineStr">
         <is>
           <t>9ea7e1a3-859f-438a-b3fc-0ff0de0e315f</t>
         </is>
@@ -8832,125 +8873,130 @@
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E97" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E97" s="1" t="inlineStr">
+      <c r="F97" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F97" s="1" t="inlineStr">
+      <c r="G97" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G97" s="1" t="inlineStr">
+      <c r="H97" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H97" s="1" t="inlineStr">
+      <c r="I97" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I97" s="1" t="inlineStr">
+      <c r="J97" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J97" s="1" t="inlineStr">
+      <c r="K97" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K97" s="1" t="inlineStr">
+      <c r="L97" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L97" s="1" t="inlineStr">
+      <c r="M97" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M97" s="1" t="inlineStr">
+      <c r="N97" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N97" s="1" t="inlineStr">
+      <c r="O97" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O97" s="1" t="inlineStr">
+      <c r="P97" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P97" s="1" t="inlineStr">
+      <c r="Q97" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q97" s="1" t="inlineStr">
+      <c r="R97" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R97" s="1" t="inlineStr">
+      <c r="S97" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S97" s="1" t="inlineStr">
+      <c r="T97" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T97" s="1" t="inlineStr">
+      <c r="U97" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U97" s="1" t="inlineStr">
+      <c r="V97" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V97" s="1" t="inlineStr">
+      <c r="W97" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W97" s="1" t="inlineStr">
+      <c r="X97" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X97" s="1" t="inlineStr">
+      <c r="Y97" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y97" s="1" t="inlineStr">
+      <c r="Z97" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z97" s="1" t="inlineStr">
+      <c r="AA97" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA97" s="1" t="inlineStr">
+      <c r="AB97" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB97" s="1" t="inlineStr">
+      <c r="AC97" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -8974,45 +9020,50 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
+          <t>b,b+1</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
           <t>Gigaton Start Up</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>Gigaton Start Up</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr">
+      <c r="P98" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr">
+      <c r="Q98" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr">
+      <c r="R98" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr">
+      <c r="S98" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
+      <c r="T98" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y98" t="inlineStr">
+      <c r="Z98" t="inlineStr">
         <is>
           <t>d1938783-b653-4c21-91d7-5303ce4b61cb</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
+      <c r="AA98" t="inlineStr">
         <is>
           <t>67a32d45-116c-42ad-88df-89b38e4ca9aa</t>
         </is>
@@ -9029,57 +9080,57 @@
           <t>hcf,b,db,d,df,f,uf,u,ub</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>– Wind Up</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>Gigaton Start Up – Wind Up</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr">
+      <c r="P99" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
+      <c r="Q99" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr">
+      <c r="R99" t="inlineStr">
         <is>
           <t>-,-</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr">
+      <c r="S99" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
+      <c r="T99" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="W99" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>Can be repeated up to 5 times.</t>
         </is>
       </c>
-      <c r="Y99" t="inlineStr">
+      <c r="Z99" t="inlineStr">
         <is>
           <t>1f65d946-be2a-4bb4-9a27-18e4ad27b7a8</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
+      <c r="AA99" t="inlineStr">
         <is>
           <t>99aa8796-5bbe-4d4a-8523-9278daf2c772</t>
         </is>
       </c>
-      <c r="AA99" t="inlineStr">
+      <c r="AB99" t="inlineStr">
         <is>
           <t>d1938783-b653-4c21-91d7-5303ce4b61cb</t>
         </is>
@@ -9096,87 +9147,87 @@
           <t>hcf,b,db,d,df,f,uf,u,ub,1</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>–– Gigaton Punch</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>Gigaton Start Up – Wind Up – Gigaton Punch</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="K100" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr">
+      <c r="N100" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr">
+      <c r="O100" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O100" t="inlineStr">
+      <c r="P100" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr">
+      <c r="Q100" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr">
+      <c r="R100" t="inlineStr">
         <is>
           <t>-,-,40</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr">
+      <c r="S100" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr">
+      <c r="T100" t="inlineStr">
         <is>
           <t>--!</t>
         </is>
       </c>
-      <c r="W100" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>Damage increases to 60, 80 and 199 with each extra Wind Up. Becomes Unblockable after 2 Wind Ups.</t>
         </is>
       </c>
-      <c r="Y100" t="inlineStr">
+      <c r="Z100" t="inlineStr">
         <is>
           <t>5effdb03-d23f-4671-8daa-b173c35d0ee4</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
+      <c r="AA100" t="inlineStr">
         <is>
           <t>8ae507ae-80ca-4f99-8564-71283564636c</t>
         </is>
       </c>
-      <c r="AA100" t="inlineStr">
+      <c r="AB100" t="inlineStr">
         <is>
           <t>1f65d946-be2a-4bb4-9a27-18e4ad27b7a8</t>
         </is>
@@ -9208,125 +9259,130 @@
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E103" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E103" s="1" t="inlineStr">
+      <c r="F103" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F103" s="1" t="inlineStr">
+      <c r="G103" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G103" s="1" t="inlineStr">
+      <c r="H103" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H103" s="1" t="inlineStr">
+      <c r="I103" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I103" s="1" t="inlineStr">
+      <c r="J103" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J103" s="1" t="inlineStr">
+      <c r="K103" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K103" s="1" t="inlineStr">
+      <c r="L103" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L103" s="1" t="inlineStr">
+      <c r="M103" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M103" s="1" t="inlineStr">
+      <c r="N103" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N103" s="1" t="inlineStr">
+      <c r="O103" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O103" s="1" t="inlineStr">
+      <c r="P103" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P103" s="1" t="inlineStr">
+      <c r="Q103" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q103" s="1" t="inlineStr">
+      <c r="R103" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R103" s="1" t="inlineStr">
+      <c r="S103" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S103" s="1" t="inlineStr">
+      <c r="T103" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T103" s="1" t="inlineStr">
+      <c r="U103" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U103" s="1" t="inlineStr">
+      <c r="V103" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V103" s="1" t="inlineStr">
+      <c r="W103" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W103" s="1" t="inlineStr">
+      <c r="X103" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X103" s="1" t="inlineStr">
+      <c r="Y103" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y103" s="1" t="inlineStr">
+      <c r="Z103" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z103" s="1" t="inlineStr">
+      <c r="AA103" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA103" s="1" t="inlineStr">
+      <c r="AB103" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB103" s="1" t="inlineStr">
+      <c r="AC103" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -9343,42 +9399,42 @@
           <t>D+2,1,1,1,2,1,2,1,1+2,1+2</t>
         </is>
       </c>
-      <c r="O104" t="inlineStr">
+      <c r="P104" t="inlineStr">
         <is>
           <t>10,6,5,7,7,6,6,8,21,25</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr">
+      <c r="Q104" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="Q104" t="inlineStr">
+      <c r="R104" t="inlineStr">
         <is>
           <t>10,6,5,7,7,6,6,8,21,25</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr">
+      <c r="S104" t="inlineStr">
         <is>
           <t>sLLmmmmmmm</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr">
+      <c r="T104" t="inlineStr">
         <is>
           <t>sLLmmmmmmm</t>
         </is>
       </c>
-      <c r="Y104" t="inlineStr">
+      <c r="Z104" t="inlineStr">
         <is>
           <t>cedd2a7b-61d7-42fe-9349-42a2b1503d3f</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
+      <c r="AA104" t="inlineStr">
         <is>
           <t>cedd2a7b-61d7-42fe-9349-42a2b1503d3f</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
+      <c r="AC104" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -9395,42 +9451,42 @@
           <t>D+2,1,1,1,2,1,2,1,d+1+2,1+2</t>
         </is>
       </c>
-      <c r="O105" t="inlineStr">
+      <c r="P105" t="inlineStr">
         <is>
           <t>10,6,5,7,7,6,6,8,12,35</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr">
+      <c r="Q105" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
-      <c r="Q105" t="inlineStr">
+      <c r="R105" t="inlineStr">
         <is>
           <t>10,6,5,7,7,6,6,8,12,35</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr">
+      <c r="S105" t="inlineStr">
         <is>
           <t>sLLmmmmmlm</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr">
+      <c r="T105" t="inlineStr">
         <is>
           <t>sLLmmmmmlm</t>
         </is>
       </c>
-      <c r="Y105" t="inlineStr">
+      <c r="Z105" t="inlineStr">
         <is>
           <t>46414757-6bbc-43ff-bcce-43bb3e815b75</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
+      <c r="AA105" t="inlineStr">
         <is>
           <t>46414757-6bbc-43ff-bcce-43bb3e815b75</t>
         </is>
       </c>
-      <c r="AB105" t="inlineStr">
+      <c r="AC105" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -9447,42 +9503,42 @@
           <t>uf+1,1,4,3,4,1,2,1,1+2,1+2</t>
         </is>
       </c>
-      <c r="O106" t="inlineStr">
+      <c r="P106" t="inlineStr">
         <is>
           <t>15,8,5,5,5,8,6,8,21,25</t>
         </is>
       </c>
-      <c r="P106" t="inlineStr">
+      <c r="Q106" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
-      <c r="Q106" t="inlineStr">
+      <c r="R106" t="inlineStr">
         <is>
           <t>15,8,5,5,5,8,6,8,21,25</t>
         </is>
       </c>
-      <c r="R106" t="inlineStr">
+      <c r="S106" t="inlineStr">
         <is>
           <t>hmLLLmmmmm</t>
         </is>
       </c>
-      <c r="S106" t="inlineStr">
+      <c r="T106" t="inlineStr">
         <is>
           <t>hmLLLmmmmm</t>
         </is>
       </c>
-      <c r="Y106" t="inlineStr">
+      <c r="Z106" t="inlineStr">
         <is>
           <t>66ed2d10-6ef0-489d-ad01-ab4680052d18</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
+      <c r="AA106" t="inlineStr">
         <is>
           <t>66ed2d10-6ef0-489d-ad01-ab4680052d18</t>
         </is>
       </c>
-      <c r="AB106" t="inlineStr">
+      <c r="AC106" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -9499,42 +9555,42 @@
           <t>uf+1,1,4,3,4,12,1,d+1+2,1+2</t>
         </is>
       </c>
-      <c r="O107" t="inlineStr">
+      <c r="P107" t="inlineStr">
         <is>
           <t>15,8,5,5,5,8,6,8,12,35</t>
         </is>
       </c>
-      <c r="P107" t="inlineStr">
+      <c r="Q107" t="inlineStr">
         <is>
           <t>107</t>
         </is>
       </c>
-      <c r="Q107" t="inlineStr">
+      <c r="R107" t="inlineStr">
         <is>
           <t>15,8,5,5,5,8,6,8,12,35</t>
         </is>
       </c>
-      <c r="R107" t="inlineStr">
+      <c r="S107" t="inlineStr">
         <is>
           <t>hmLLLmmmlm</t>
         </is>
       </c>
-      <c r="S107" t="inlineStr">
+      <c r="T107" t="inlineStr">
         <is>
           <t>hmLLLmmmlm</t>
         </is>
       </c>
-      <c r="Y107" t="inlineStr">
+      <c r="Z107" t="inlineStr">
         <is>
           <t>bfdf582e-6190-406a-b25c-eee25e104050</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
+      <c r="AA107" t="inlineStr">
         <is>
           <t>bfdf582e-6190-406a-b25c-eee25e104050</t>
         </is>
       </c>
-      <c r="AB107" t="inlineStr">
+      <c r="AC107" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>

--- a/sources/jack2_step8.xlsx
+++ b/sources/jack2_step8.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC107"/>
+  <dimension ref="A1:AC112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" min="1" max="1"/>
@@ -425,7 +425,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col hidden="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="53" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col hidden="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
@@ -4291,6 +4291,16 @@
           <t>b,db,d,DF+1</t>
         </is>
       </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>hcf,DF+1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>hcf,DF+1</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>Debugger</t>
@@ -4405,35 +4415,15 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Wind Up</t>
+          <t>Wind Up (1 Rotation)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wind Up</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>Wind Up (1 Rotation)</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4462,12 +4452,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gigaton Punch</t>
+          <t>– Gigaton Punch (1 Rotation)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wind Up – Gigaton Punch</t>
+          <t>Wind Up (1 Rotation) – Gigaton Punch (1 Rotation)</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4517,7 +4507,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>-,20</t>
+          <t>20</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -4527,7 +4517,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>-m</t>
+          <t>m</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -4554,1316 +4544,891 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>– DF+1</t>
+          <t>ccw,db,d</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>hcf,DF+1</t>
+          <t>ccw,db,d</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Debugger</t>
+          <t>Wind Up (2 Rotations)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wind Up – Debugger</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>-45</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>-45</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>-,25</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>-L</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>Wind Up (2 Rotations)</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>With b,b+1 input, full 2nd rotation command is b,b+1,b,db,d,df</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>bfcd8070-9fe9-4f68-b19e-bddec360b30a</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>bc7743df-d62c-4baf-90d6-ca367a954aba</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>c03fb65b-aaac-4006-8e2b-0a9f8c08fd8f</t>
+          <t>1f65d946-be2a-4bb4-9a27-18e4ad27b7a8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DF+1,2,1,2</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DF+1,2,1,2</t>
+          <t>ccw,db,d,1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Uppercut Rush</t>
+          <t>– Gigaton Punch (2 Rotations)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Uppercut Rush</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>14</t>
+          <t>Wind Up (2 Rotations) – Gigaton Punch (2 Rotations)</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-11 -7 -9 -2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>-11 -7 -9 -2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>KD +4 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>KD +4 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>KD +4 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>KD +4 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>10,15,10,15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>10,15,10,15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>mmmm</t>
+          <t>!</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>mmmm</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>JGc RC</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>Juggles on the last hit if the first hit was a counter hit.</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>4f881878-519e-4f9f-bb13-ebe8511b7e9f</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>bf72dea8-4c41-4bb6-9420-9305240a53e3</t>
+          <t>5effdb03-d23f-4671-8daa-b173c35d0ee4</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>1f65d946-be2a-4bb4-9a27-18e4ad27b7a8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DF,1,2,1</t>
+          <t>ccw,ccw,db,d</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DF,1,2,1</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>FC+DF+1,2,1</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>FC+DF+1,2,1</t>
+          <t>ccw,ccw,db,d</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Quick Upper Rush</t>
+          <t>Wind Up (3 Rotations)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Quick Upper Rush</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>-6 -8 -2</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>-6 -8 -2</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>+5 +2 +9</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>+5 +2 +9</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>+5 +2 +9</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>+5 +2 +9</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>15,12,15</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>15,12,15</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>mmm</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>mmm</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>JGc RC</t>
+          <t>Wind Up (3 Rotations)</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Juggles on the last hit if the first hit was a counter hit.</t>
+          <t>With b,b+1 input, full 3rd rotation command is b,b+1,ccw,b,db,d</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>7507a693-7948-45eb-a05e-3707d923e16d</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>b30faab6-54e4-4123-ab0b-5fb12faa3be2</t>
+          <t>f6c85458-dd91-4d88-91f1-9a557e0c3420</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FC+df+1,2,1</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FC+df+1,2,1</t>
+          <t>ccw,ccw,db,d,1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Windmill</t>
+          <t>– Gigaton Punch (3 Rotations)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Windmill</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>24</t>
+          <t>Wind Up (3 Rotations) – Gigaton Punch (3 Rotations)</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>-22 -22 -2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>-22 -22 -2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-12 -12 -12</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>-12 -12 -12</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>-12 -12 -12</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>-12 -12 -12</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>10,15,10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>60</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>10,15,10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>!</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>dbb96ec3-9f0f-4e57-b4ca-8de7e5046661</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>1c7f46c4-6ab3-4fdd-90e3-5f642409d3af</t>
+          <t>e63a69f8-5fec-47ed-a05a-1068334010ce</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>f6c85458-dd91-4d88-91f1-9a557e0c3420</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>– 1</t>
+          <t>ccw,ccw,ccw,db,d</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FC+df+1,2,1,1</t>
+          <t>ccw,ccw,ccw,db,d</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>– Windmill Backhand</t>
+          <t>Wind Up (4 Rotations)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Windmill – Windmill Backhand</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>+20</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>-22 -22 -2 +20</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>-12 -12 -12 KD</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>-12 -12 -12 KD</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>10,15,10,30</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>mmmh</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>CF GB</t>
+          <t>Wind Up (4 Rotations)</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>82838a4d-d558-42b7-ab73-e05d17ef4b08</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>e3e5f6b7-4929-4a52-8c31-e6806f1334ee</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>dbb96ec3-9f0f-4e57-b4ca-8de7e5046661</t>
+          <t>c0f65cc6-5cf3-4384-bf35-b9b00543eb08</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DF,1,2</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DF,1,2</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>FC+DF+1,2</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>FC+DF+1,2</t>
+          <t>ccw,ccw,ccw,db,d,1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Medium Hammer Rush</t>
+          <t>– Gigaton Punch (4 Rotations)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Medium Hammer Rush</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>Wind Up (4 Rotations) – Gigaton Punch (4 Rotations)</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-6 -8</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>-6 -8</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>+5 +2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>+5 +2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>+5 +2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>+5 +2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>15,12</t>
+          <t>80</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>15,12</t>
+          <t>80</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>!</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>53b77124-e72d-4f20-ae78-8225f04ac648</t>
+          <t>0b650a95-0538-44cb-a60f-505df7041965</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>c0f65cc6-5cf3-4384-bf35-b9b00543eb08</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>– d+1</t>
+          <t>ccw,ccw,ccw,ccw,db,d</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DF,1,2,d+1</t>
+          <t>ccw,ccw,ccw,ccw,db,d</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>– Low Punch</t>
+          <t>Wind Up (5 Rotations)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Medium Hammer Rush – Low Punch</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>-17</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>-6 -8 -17</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>-7</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>+5 +2 -7</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>-7</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>+5 +2 -7</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>15,12,8</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>mmL</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>Wind Up (5 Rotations)</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>29dfa2dc-0160-4e71-b110-03e973136272</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>be700e61-7fed-40b2-a16a-4b062cedd1c9</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
+          <t>27d20b09-dd03-41a8-a3e5-9fb3bbc279ad</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>– df+1</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DF,1,2,df+1</t>
+          <t>ccw,ccw,ccw,ccw,db,d,1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>– Mid Punch</t>
+          <t>– Gigaton Punch (5 Rotations)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Medium Hammer Rush – Mid Punch</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>Wind Up (5 Rotations) – Gigaton Punch (5 Rotations)</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>-6 -8 -1</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>+5 +2 +10</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>+5 +2 +10</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>199</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>199</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>15,12,15</t>
+          <t>199</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>!</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>mmm</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>eb9bbfe4-68c3-4e58-baf7-821687138e91</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>636b5aa8-46de-464e-81e9-d0bcfa43dc73</t>
+          <t>e17fd2d9-47bc-4541-8a57-8d670b1585de</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
+          <t>27d20b09-dd03-41a8-a3e5-9fb3bbc279ad</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>– f+1</t>
+          <t>ccw,ccw,ccw,ccw,ccw,db,d</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DF,1,2,f+1</t>
+          <t>ccw,ccw,ccw,ccw,ccw,db,d</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>– High Punch</t>
+          <t>Wind Up (8 Rotations)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Medium Hammer Rush – High Punch</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>-17</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>-6 -8 -17</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>+5 +2 -5</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>+5 +2 -5</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>15,12,12</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>mmh</t>
+          <t>Wind Up (8 Rotations)</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Completes 8 rotations automatically. No Gigaton Punch follow-up.</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>897a7dd1-1093-48ff-85f1-bebca88601ea</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>96ffff19-8555-4463-82fe-458f7c0c053b</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
+          <t>15f7632c-c216-4131-a173-898bf20c3023</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FC+1,1,1,2</t>
+          <t>DF+1,2,1,2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FC+1,1,1,2</t>
+          <t>DF+1,2,1,2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hammer Rush</t>
+          <t>Uppercut Rush</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hammer Rush</t>
+          <t>Uppercut Rush</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>-8 +1 -12 -8</t>
+          <t>-11 -7 -9 -2</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>-8 +1 -12 -8</t>
+          <t>-11 -7 -9 -2</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1</t>
+          <t>KD +4 +2 +9</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1</t>
+          <t>KD +4 +2 +9</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1</t>
+          <t>KD +4 +2 +9</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1</t>
+          <t>KD +4 +2 +9</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>10,8,12,12</t>
+          <t>10,15,10,15</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>50</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>10,8,12,12</t>
+          <t>10,15,10,15</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>LLmm</t>
+          <t>mmmm</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>LLmm</t>
+          <t>mmmm</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>JGc RC</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Juggles on the last hit if the first hit was a counter hit.</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
+          <t>4f881878-519e-4f9f-bb13-ebe8511b7e9f</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>87b157c8-bac6-4b55-a543-03b3e5c1c00f</t>
+          <t>bf72dea8-4c41-4bb6-9420-9305240a53e3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>– d+1</t>
+          <t>DF,1,2,1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FC+1,1,1,2,d+1</t>
+          <t>DF,1,2,1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>FC+DF+1,2,1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>FC+DF+1,2,1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>– Low Punch</t>
+          <t>Quick Upper Rush</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hammer Rush – Low Punch</t>
+          <t>Quick Upper Rush</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-6 -8 -2</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>-8 +1 -12 -8 -17</t>
+          <t>-6 -8 -2</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>+5 +2 +9</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1 -7</t>
+          <t>+5 +2 +9</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>+5 +2 +9</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1 -7</t>
+          <t>+5 +2 +9</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15,12,15</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>42</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>10,8,12,12,8</t>
+          <t>15,12,15</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>LLmmL</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>JGc RC</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Juggles on the last hit if the first hit was a counter hit.</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>acb95787-cedc-4b5b-b8fb-50a3e72d4b5b</t>
+          <t>7507a693-7948-45eb-a05e-3707d923e16d</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>19e50734-0a3e-439a-bb45-d0541eae3da2</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
+          <t>b30faab6-54e4-4123-ab0b-5fb12faa3be2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>– df+1</t>
+          <t>FC+df+1,2,1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FC+1,1,1,2,df+1</t>
+          <t>FC+df+1,2,1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>– Mid Punch</t>
+          <t>Windmill</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hammer Rush – Mid Punch</t>
+          <t>Windmill</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-22 -22 -2</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>-8 +1 -12 -8 -1</t>
+          <t>-22 -22 -2</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>-12 -12 -12</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1 +10</t>
+          <t>-12 -12 -12</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>-12 -12 -12</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1 +10</t>
+          <t>-12 -12 -12</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10,15,10</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>10,8,12,12,15</t>
+          <t>10,15,10</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>LLmmm</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>756e1d64-081b-4d25-aaa0-fa5c3b7a738f</t>
+          <t>dbb96ec3-9f0f-4e57-b4ca-8de7e5046661</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>ecd60ebe-4c07-4ca2-a44b-3748905360dd</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
+          <t>1c7f46c4-6ab3-4fdd-90e3-5f642409d3af</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>– f+1</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FC+1,1,1,2,f+1</t>
+          <t>FC+df+1,2,1,1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>– High Punch</t>
+          <t>– Windmill Backhand</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hammer Rush – High Punch</t>
+          <t>Windmill – Windmill Backhand</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>+20</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>-8 +1 -12 -8 -17</t>
+          <t>-22 -22 -2 +20</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1 -5</t>
+          <t>-12 -12 -12 KD</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1 -5</t>
+          <t>-12 -12 -12 KD</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>10,8,12,12,12</t>
+          <t>10,15,10,30</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -5873,109 +5438,124 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>LLmmh</t>
+          <t>mmmh</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>CF GB</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>ac1b3ebe-7028-47a0-be65-5eb121dab8bc</t>
+          <t>82838a4d-d558-42b7-ab73-e05d17ef4b08</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>fe5b804b-6426-463e-b283-4eb22f9998b3</t>
+          <t>e3e5f6b7-4929-4a52-8c31-e6806f1334ee</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
+          <t>dbb96ec3-9f0f-4e57-b4ca-8de7e5046661</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FC+1,2</t>
+          <t>DF,1,2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FC+1,2</t>
+          <t>DF,1,2</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>FC+DF+1,2</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>FC+DF+1,2</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Low Punch - Megaton Punch</t>
+          <t>Medium Hammer Rush</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Low Punch - Megaton Punch</t>
+          <t>Medium Hammer Rush</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>-8 -14</t>
+          <t>-6 -8</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>-8 -14</t>
+          <t>-6 -8</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>+2 KD</t>
+          <t>+5 +2</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>+2 KD</t>
+          <t>+5 +2</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>+2 KD</t>
+          <t>+5 +2</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>+2 KD</t>
+          <t>+5 +2</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>10,25</t>
+          <t>15,12</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>10,25</t>
+          <t>15,12</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>Lm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>Lm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
@@ -5985,151 +5565,141 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>06ab7954-5d39-49cc-91e3-02c54893dd53</t>
+          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>a769fb07-8a59-436e-a5fb-3acd34e8e01d</t>
+          <t>53b77124-e72d-4f20-ae78-8225f04ac648</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SS+1</t>
+          <t>– d+1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SS+1</t>
+          <t>DF,1,2,d+1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Jack Hammer</t>
+          <t>– Low Punch</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Jack Hammer</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>32</t>
+          <t>Medium Hammer Rush – Low Punch</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6 -8 -17</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +2 -7</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +2 -7</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15,12,8</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>L</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mmL</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>BN GB</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>41456c1a-f3a2-468f-b0ee-ee2032bb78c8</t>
+          <t>29dfa2dc-0160-4e71-b110-03e973136272</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>de86a0e0-55fd-41e5-a239-a7685c39edbd</t>
+          <t>be700e61-7fed-40b2-a16a-4b062cedd1c9</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SS+1+2</t>
+          <t>– df+1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SS+1+2</t>
+          <t>DF,1,2,df+1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Double Knuckle Swing</t>
+          <t>– Mid Punch</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Double Knuckle Swing</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>19</t>
+          <t>Medium Hammer Rush – Mid Punch</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6139,425 +5709,430 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-6 -8 -1</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +2 +10</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +2 +10</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15,12,15</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>m</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>mmm</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15c368e0-8f76-42a0-bbea-ef3cc510e19c</t>
+          <t>eb9bbfe4-68c3-4e58-baf7-821687138e91</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2f8a7e04-7a60-430d-bc0a-6a55ed0d3427</t>
+          <t>636b5aa8-46de-464e-81e9-d0bcfa43dc73</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1+2&lt;1+2</t>
+          <t>– f+1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1+2&lt;1+2</t>
+          <t>DF,1,2,f+1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hammer Knuckle - Double Uppercut</t>
+          <t>– High Punch</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hammer Knuckle - Double Uppercut</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
+          <t>Medium Hammer Rush – High Punch</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>-15 -20</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>-15 -20</t>
+          <t>-6 -8 -17</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+5 +2 -5</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+5 +2 -5</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>21,22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>21,22</t>
+          <t>15,12,12</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>h</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>JG</t>
+          <t>mmh</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>54667fc1-c443-4001-a9d7-46c1d391bc4d</t>
+          <t>897a7dd1-1093-48ff-85f1-bebca88601ea</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>36af744c-98c3-48c0-bea9-c96c61093c26</t>
+          <t>96ffff19-8555-4463-82fe-458f7c0c053b</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>WS+1+2&lt;1+2</t>
+          <t>FC+1,1,1,2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WS+1+2&lt;1+2</t>
+          <t>FC+1,1,1,2</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Double Uppercut - Hammer Knuckle</t>
+          <t>Hammer Rush</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Double Uppercut - Hammer Knuckle</t>
+          <t>Hammer Rush</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>-15 -16</t>
+          <t>-8 +1 -12 -8</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>-15 -16</t>
+          <t>-8 +1 -12 -8</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+2 +12 -1 +1</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+2 +12 -1 +1</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+2 +12 -1 +1</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+2 +12 -1 +1</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>21,17</t>
+          <t>10,8,12,12</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>42</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>21,17</t>
+          <t>10,8,12,12</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>LLmm</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>LLmm</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14470b5f-e125-4262-857b-20fa6db24ee3</t>
+          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>45985eea-a458-447f-9b9d-941ed088446a</t>
+          <t>87b157c8-bac6-4b55-a543-03b3e5c1c00f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>f+1+2</t>
+          <t>– d+1</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>f+1+2</t>
+          <t>FC+1,1,1,2,d+1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Arm Scissors</t>
+          <t>– Low Punch</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Arm Scissors</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>Hammer Rush – Low Punch</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-8 +1 -12 -8 -17</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2 +12 -1 +1 -7</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2 +12 -1 +1 -7</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10,8,12,12,8</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>L</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>LLmmL</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
+          <t>acb95787-cedc-4b5b-b8fb-50a3e72d4b5b</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>f51b4cde-994c-422f-b3e6-3e932f7d87ff</t>
+          <t>19e50734-0a3e-439a-bb45-d0541eae3da2</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>– 1+2</t>
+          <t>– df+1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>f+1+2,1+2</t>
+          <t>FC+1,1,1,2,df+1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>– Cross Cut Saw</t>
+          <t>– Mid Punch</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Arm Scissors – Cross Cut Saw</t>
+          <t>Hammer Rush – Mid Punch</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>-10 -14</t>
+          <t>-8 +1 -12 -8 -1</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+2 +12 -1 +1 +10</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+2 +12 -1 +1 +10</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -6572,17 +6147,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>17,15</t>
+          <t>10,8,12,12,15</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>m</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>LLmmm</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
@@ -6592,273 +6167,258 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>acab70ca-8813-48c6-907e-58ba82b57685</t>
+          <t>756e1d64-081b-4d25-aaa0-fa5c3b7a738f</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>e7af4cd0-902b-4b89-9c43-ea9365bec42c</t>
+          <t>ecd60ebe-4c07-4ca2-a44b-3748905360dd</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
+          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>– ~df+2</t>
+          <t>– f+1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>f+1+2~df+2</t>
+          <t>FC+1,1,1,2,f+1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>– Megaton Punch</t>
+          <t>– High Punch</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Arm Scissors – Megaton Punch</t>
+          <t>Hammer Rush – High Punch</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>-10 -19</t>
+          <t>-8 +1 -12 -8 -17</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+2 +12 -1 +1 -5</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+2 +12 -1 +1 -5</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>17,25</t>
+          <t>10,8,12,12,12</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>h</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>LLmmh</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>773af138-28f0-48ff-9b0e-97e83d2d8d3f</t>
+          <t>ac1b3ebe-7028-47a0-be65-5eb121dab8bc</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>b671f9fe-a460-4157-8300-00379e99322d</t>
+          <t>fe5b804b-6426-463e-b283-4eb22f9998b3</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
+          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>d+1+2</t>
+          <t>FC+1,2</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>d+1+2</t>
+          <t>FC+1,2</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bravo Knuckle</t>
+          <t>Low Punch - Megaton Punch</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bravo Knuckle</t>
+          <t>Low Punch - Megaton Punch</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>-8 -14</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>-8 -14</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2 KD</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2 KD</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2 KD</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2 KD</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>10,25</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>10,25</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Lm</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Lm</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>JG GB</t>
-        </is>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>When tagging in Bryan Fury hit 2 to grab the opponent in mid air and do a Fisherman's Slam. Total damage is 21,21.</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>f79bf7d8-dcd1-4a58-883f-38e113a7b9e1</t>
+          <t>06ab7954-5d39-49cc-91e3-02c54893dd53</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2ecc5ad9-b4ca-485a-884a-0301a91b3509</t>
+          <t>a769fb07-8a59-436e-a5fb-3acd34e8e01d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FC+1+2</t>
+          <t>SS+1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FC+1+2</t>
+          <t>SS+1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cross Cut Saw</t>
+          <t>Jack Hammer</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Cross Cut Saw</t>
+          <t>Jack Hammer</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6883,562 +6443,532 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>m</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>m</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>BN GB</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>23e71f4e-0ab8-4ddc-89c1-4b2fe81234cc</t>
+          <t>41456c1a-f3a2-468f-b0ee-ee2032bb78c8</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>52606470-ef56-4c68-a311-9fe12c9a5f23</t>
+          <t>de86a0e0-55fd-41e5-a239-a7685c39edbd</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DF,2,1,2</t>
+          <t>SS+1+2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DF,2,1,2</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>FC+DF+2,1,2</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>FC+DF+2,1,2</t>
+          <t>SS+1+2</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Quick Uppercut Rush</t>
+          <t>Double Knuckle Swing</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Quick Uppercut Rush</t>
+          <t>Double Knuckle Swing</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>-9 -2 -9</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>-9 -2 -9</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>-2 +10 +2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>-2 +10 +2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>-2 +10 +2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>-2 +10 +2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>15,10,15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>15,10,15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>h</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>mmm</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>JGc RC</t>
-        </is>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>Juggles on the last hit if the first hit was a counter hit.</t>
+          <t>h</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>38964142-4e38-457c-9a6d-9ef0fcf12cd4</t>
+          <t>15c368e0-8f76-42a0-bbea-ef3cc510e19c</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>8efe400a-6435-45e4-92f5-b9e1d4fd9595</t>
+          <t>2f8a7e04-7a60-430d-bc0a-6a55ed0d3427</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DF+2,1,2,1</t>
+          <t>1+2&lt;1+2</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DF+2,1,2,1</t>
+          <t>1+2&lt;1+2</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hammer Uppercut Rush</t>
+          <t>Hammer Knuckle - Double Uppercut</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Hammer Uppercut Rush</t>
+          <t>Hammer Knuckle - Double Uppercut</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>-11 -6 -9 -1</t>
+          <t>-15 -20</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>-11 -6 -9 -1</t>
+          <t>-15 -20</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>KD +5 +3 +10</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>KD +5 +3 +10</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>KD +5 +3 +10</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>KD +5 +3 +10</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>10,15,12,15</t>
+          <t>21,22</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>43</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>10,15,12,15</t>
+          <t>21,22</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>mmmm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>mmmm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>JG RC</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>f62fd939-223c-47b4-982b-aecff23cfca4</t>
+          <t>54667fc1-c443-4001-a9d7-46c1d391bc4d</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>e85a400e-73a4-495b-917a-82244da3681f</t>
+          <t>36af744c-98c3-48c0-bea9-c96c61093c26</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>f,f+2</t>
+          <t>WS+1+2&lt;1+2</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>f,f+2</t>
+          <t>WS+1+2&lt;1+2</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Atomic Hook</t>
+          <t>Double Uppercut - Hammer Knuckle</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Atomic Hook</t>
+          <t>Double Uppercut - Hammer Knuckle</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-15 -16</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-15 -16</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21,17</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>38</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21,17</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>JG</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>e3ef4e95-cdea-4525-83df-74474e814b2a</t>
+          <t>14470b5f-e125-4262-857b-20fa6db24ee3</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>e14fe285-946c-414b-88e4-d7e2f3af2745</t>
+          <t>45985eea-a458-447f-9b9d-941ed088446a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2,1,2</t>
+          <t>f+1+2</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2,1,2</t>
+          <t>f+1+2</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Punch - Elbow - Uppercut</t>
+          <t>Arm Scissors</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Punch - Elbow - Uppercut</t>
+          <t>Arm Scissors</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>0 0 -15</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>0 0 -15</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>+7 +2 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>+7 +2 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>+7 +2 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>+7 +2 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>12,15,20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>12,15,20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>JG</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>b51b9f18-a0d7-4234-b6c4-e0db8e729094</t>
+          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>06e4e99f-b024-4491-a080-43e24bdee8bc</t>
+          <t>f51b4cde-994c-422f-b3e6-3e932f7d87ff</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DF,2</t>
+          <t>– 1+2</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DF,2</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>FC+df+2</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>FC+df+2</t>
+          <t>f+1+2,1+2</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Short Hammer Rush</t>
+          <t>– Cross Cut Saw</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Short Hammer Rush</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>Arm Scissors – Cross Cut Saw</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-10 -14</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17,15</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>l</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
@@ -7448,94 +6978,99 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
+          <t>acab70ca-8813-48c6-907e-58ba82b57685</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>d79c3cf7-3a6f-4c0a-b31a-e35de47e6878</t>
+          <t>e7af4cd0-902b-4b89-9c43-ea9365bec42c</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>– d+1</t>
+          <t>– ~df+2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>DF,2,d+1</t>
+          <t>f+1+2~df+2</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>– Low Punch</t>
+          <t>– Megaton Punch</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Short Hammer Rush – Low Punch</t>
+          <t>Arm Scissors – Megaton Punch</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>-13 -17</t>
+          <t>-10 -19</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>-2 -7</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>-2 -7</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>10,8</t>
+          <t>17,25</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>m</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>mL</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="W80" t="inlineStr">
@@ -7545,89 +7080,94 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>82744639-21bd-464e-acb0-fb430a833b71</t>
+          <t>773af138-28f0-48ff-9b0e-97e83d2d8d3f</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>da44dd7b-4cdb-4823-a817-06318a68273c</t>
+          <t>b671f9fe-a460-4157-8300-00379e99322d</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
+          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>– df+1</t>
+          <t>d+1+2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DF,2,df+1</t>
+          <t>d+1+2</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>– Mid Punch</t>
+          <t>Bravo Knuckle</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Short Hammer Rush – Mid Punch</t>
+          <t>Bravo Knuckle</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-23</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>-13 -1</t>
+          <t>-23</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>-2 +10</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>-2 +10</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>10,15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -7637,375 +7177,395 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>JG GB</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>When tagging in Bryan Fury hit 2 to grab the opponent in mid air and do a Fisherman's Slam. Total damage is 21,21.</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>9cba188e-9985-4f96-83e4-7db5474781d2</t>
+          <t>f79bf7d8-dcd1-4a58-883f-38e113a7b9e1</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>51f0fb87-39b1-45cd-ab41-c081312a5d9b</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
+          <t>2ecc5ad9-b4ca-485a-884a-0301a91b3509</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>– f+1</t>
+          <t>FC+1+2</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DF,2,f+1</t>
+          <t>FC+1+2</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>– High Punch</t>
+          <t>Cross Cut Saw</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Short Hammer Rush – High Punch</t>
+          <t>Cross Cut Saw</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>-13 -17</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>-2 -5</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>-2 -5</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>10,12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>l</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>mh</t>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>9dd1c03f-e1e1-4e41-b91a-88df8054ec5c</t>
+          <t>23e71f4e-0ab8-4ddc-89c1-4b2fe81234cc</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>529ea903-bd1d-4081-ab74-eb6b82eaab94</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
+          <t>52606470-ef56-4c68-a311-9fe12c9a5f23</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>b,db,d,DF+2</t>
+          <t>DF,2,1,2</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>b,db,d,DF+2</t>
+          <t>DF,2,1,2</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>FC+DF+2,1,2</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>FC+DF+2,1,2</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Megaton Punch</t>
+          <t>Quick Uppercut Rush</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Megaton Punch</t>
+          <t>Quick Uppercut Rush</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-9 -2 -9</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-9 -2 -9</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 +10 +2</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 +10 +2</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 +10 +2</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 +10 +2</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>15,10,15</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>40</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>15,10,15</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>JGc RC</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Juggles on the last hit if the first hit was a counter hit.</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>56b1623c-ef98-42a3-be49-2ebc46462a0f</t>
+          <t>38964142-4e38-457c-9a6d-9ef0fcf12cd4</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>e818b2a1-12e3-409b-8e48-4b059aaa76c0</t>
+          <t>8efe400a-6435-45e4-92f5-b9e1d4fd9595</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>f,f+3</t>
+          <t>DF+2,1,2,1</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>f,f+3</t>
+          <t>DF+2,1,2,1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Granite Stomp</t>
+          <t>Hammer Uppercut Rush</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granite Stomp</t>
+          <t>Hammer Uppercut Rush</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>-11 -6 -9 -1</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>-11 -6 -9 -1</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD +5 +3 +10</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD +5 +3 +10</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD +5 +3 +10</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD +5 +3 +10</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10,15,12,15</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>52</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10,15,12,15</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>mmmm</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>mmmm</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>JG RC</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>ee6c0589-29fe-439a-8f69-242d8e6811f6</t>
+          <t>f62fd939-223c-47b4-982b-aecff23cfca4</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>879d1a1f-95b2-4081-aa4b-dc74da0c13c6</t>
+          <t>e85a400e-73a4-495b-917a-82244da3681f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>f+3+4</t>
+          <t>f,f+2</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>f+3+4</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>FC+df+3+4</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>FC+df+3+4</t>
+          <t>f,f+2</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Giga Shoulder Ram</t>
+          <t>Atomic Hook</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Giga Shoulder Ram</t>
+          <t>Atomic Hook</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8030,693 +7590,843 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>h</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>h</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>20d7633a-2326-4494-84f9-0a235f1c2fe8</t>
+          <t>e3ef4e95-cdea-4525-83df-74474e814b2a</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>b0da65f9-bf50-406e-8de8-7db02d0abb2c</t>
+          <t>e14fe285-946c-414b-88e4-d7e2f3af2745</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DB+3,4,3,4,3,4</t>
+          <t>2,1,2</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DB+3,4,3,4,3,4</t>
+          <t>2,1,2</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cossack Kicks</t>
+          <t>Punch - Elbow - Uppercut</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cossack Kicks</t>
+          <t>Punch - Elbow - Uppercut</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>-20 -22 -20 -22...</t>
+          <t>0 0 -15</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>-20 -22 -20 -22...</t>
+          <t>0 0 -15</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>-9 -11 -9 -11...</t>
+          <t>+7 +2 KD</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>-9 -11 -9 -11...</t>
+          <t>+7 +2 KD</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>-9 -11 -9 -11...</t>
+          <t>+7 +2 KD</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>-9 -11 -9 -11...</t>
+          <t>+7 +2 KD</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>18,12,10,12,12,12</t>
+          <t>12,15,20</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>47</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>18,12,10,12,12,12</t>
+          <t>12,15,20</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>LLLLLL</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>LLLLLL</t>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>674f6841-5fbb-4b15-865f-9ab351c1a0f0</t>
+          <t>b51b9f18-a0d7-4234-b6c4-e0db8e729094</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>4c477a6b-86e6-43f8-911d-93481004b0b5</t>
+          <t>06e4e99f-b024-4491-a080-43e24bdee8bc</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>uf+3+4</t>
+          <t>DF,2</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>uf+3+4</t>
+          <t>DF,2</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>FC+df+2</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>FC+df+2</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Hip Press</t>
+          <t>Short Hammer Rush</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Hip Press</t>
+          <t>Short Hammer Rush</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>-40</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>-40</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>-40</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>-40</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>m</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>If the Hip Press Misses the opponent, Jack-2 can chain into Sit Down extentions.</t>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>3be14565-e783-4db3-9168-bf98e290f21d</t>
+          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>ce4da910-2232-4be6-a896-136d900764e1</t>
+          <t>d79c3cf7-3a6f-4c0a-b31a-e35de47e6878</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3+4</t>
+          <t>– d+1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>3+4</t>
+          <t>DF,2,d+1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sit Down</t>
+          <t>– Low Punch</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sit Down</t>
+          <t>Short Hammer Rush – Low Punch</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>-17</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>-13 -17</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>-7</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>-2 -7</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>-7</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>-2 -7</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10,8</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>L</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
+          <t>82744639-21bd-464e-acb0-fb430a833b71</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>8ff726df-3bc4-4645-98be-c2fad557ee7d</t>
+          <t>da44dd7b-4cdb-4823-a817-06318a68273c</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>– ~3+4</t>
+          <t>– df+1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>3+4~3+4</t>
+          <t>DF,2,df+1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>– Hop Hip Press</t>
+          <t>– Mid Punch</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sit Down – Hop Hip Press</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>62</t>
+          <t>Short Hammer Rush – Mid Punch</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>-13 -1</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>-34</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>-34</t>
+          <t>-2 +10</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>-34</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>-34</t>
+          <t>-2 +10</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>-,35</t>
+          <t>10,15</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>m</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>-M</t>
-        </is>
-      </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>If the Hip Press Misses the opponent, Jack-2 can chain into Sit Down extentions.</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
+          <t>9cba188e-9985-4f96-83e4-7db5474781d2</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>1f37a24d-750f-4851-a2b5-a6b9a1b4ed26</t>
+          <t>51f0fb87-39b1-45cd-ab41-c081312a5d9b</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
+          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>– B</t>
+          <t>– f+1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>3+4,B</t>
+          <t>DF,2,f+1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>– Roll Back</t>
+          <t>– High Punch</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sit Down – Roll Back</t>
+          <t>Short Hammer Rush – High Punch</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>-17</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>-13 -17</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>-2 -5</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>-2 -5</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>-,-</t>
+          <t>10,12</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>h</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>mh</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>a96a391b-b0cf-493d-a205-6511f1e34903</t>
+          <t>9dd1c03f-e1e1-4e41-b91a-88df8054ec5c</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>4f15e677-cb84-4d03-b6d8-82c26255c1d9</t>
+          <t>529ea903-bd1d-4081-ab74-eb6b82eaab94</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
+          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>– F</t>
+          <t>b,db,d,DF+2</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>3+4,F</t>
+          <t>b,db,d,DF+2</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>– Roll Forward</t>
+          <t>Megaton Punch</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sit Down – Roll Forward</t>
+          <t>Megaton Punch</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>-17</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>-17</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>KD</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>-,-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>m</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>df8e44d6-d84c-4ee6-8117-15cb0b65ceb6</t>
+          <t>56b1623c-ef98-42a3-be49-2ebc46462a0f</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>0680a704-d8c9-47e5-91a9-98babe1c15af</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
+          <t>e818b2a1-12e3-409b-8e48-4b059aaa76c0</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>– 1,2,1,2</t>
+          <t>f,f+3</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>3+4,1,2,1,2</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>2,1,2,1</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>3+4,2,1,2,1</t>
+          <t>f,f+3</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>– Sitting Punches</t>
+          <t>Granite Stomp</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sit Down – Sitting Punches</t>
+          <t>Granite Stomp</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>-45 -43 -45 -43</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>-45 -43 -45 -43</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>-35 -32 -35 -32</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>-35 -32 -35 -32</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>-35 -32 -35 -32</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>-35 -32 -35 -32</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>10,10,10,10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>-,10,10,10,10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>llll</t>
+          <t>M</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>-llll</t>
+          <t>M</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>1e575213-1523-40b8-9492-0a92235d1799</t>
+          <t>ee6c0589-29fe-439a-8f69-242d8e6811f6</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>71c8d35f-24b6-430d-abc5-2ff4c47a8f3b</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
+          <t>879d1a1f-95b2-4081-aa4b-dc74da0c13c6</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>KND d+1+2</t>
+          <t>f+3+4</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>KND d+1+2</t>
+          <t>f+3+4</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>FC+df+3+4</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>FC+df+3+4</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Spring Hammer - Sit Down</t>
+          <t>Giga Shoulder Ram</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spring Hammer - Sit Down</t>
+          <t>Giga Shoulder Ram</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>+20</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>+20</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>+14</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>+14</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>+14</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>+14</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>28</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -8731,306 +8441,392 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>9ea7e1a3-859f-438a-b3fc-0ff0de0e315f</t>
+          <t>20d7633a-2326-4494-84f9-0a235f1c2fe8</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>0066d9e6-44cc-4c22-b95a-1c01b1cb1dcb</t>
+          <t>b0da65f9-bf50-406e-8de8-7db02d0abb2c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>– 1,2,1,2</t>
+          <t>DB+3,4,3,4,3,4</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>KND d+1+2,1,2,1,2</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>2,1,2,1</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>KND d+1+2,2,1,2,1</t>
+          <t>DB+3,4,3,4,3,4</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>– Sitting Punches</t>
+          <t>Cossack Kicks</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spring Hammer - Sit Down – Sitting Punches</t>
+          <t>Cossack Kicks</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>-45 -43 -45 -43</t>
+          <t>-20 -22 -20 -22...</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>+20 -45 -43 -45 -43</t>
+          <t>-20 -22 -20 -22...</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>-35 -32 -35 -32</t>
+          <t>-9 -11 -9 -11...</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>+14 -35 -32 -35 -32</t>
+          <t>-9 -11 -9 -11...</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>-35 -32 -35 -32</t>
+          <t>-9 -11 -9 -11...</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>+14 -35 -32 -35 -32</t>
+          <t>-9 -11 -9 -11...</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>10,10,10,10</t>
+          <t>18,12,10,12,12,12</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>76</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>12,10,10,10,10</t>
+          <t>18,12,10,12,12,12</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>llll</t>
+          <t>LLLLLL</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>mllll</t>
+          <t>LLLLLL</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>eb0c424e-d4b0-438e-bfb7-164bbca1894a</t>
+          <t>674f6841-5fbb-4b15-865f-9ab351c1a0f0</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>01e88eb2-b793-4ba3-9d87-7f7b3ab33381</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>9ea7e1a3-859f-438a-b3fc-0ff0de0e315f</t>
-        </is>
-      </c>
-    </row>
-    <row r="95"/>
+          <t>4c477a6b-86e6-43f8-911d-93481004b0b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>uf+3+4</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>uf+3+4</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Hip Press</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Hip Press</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>-40</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>-40</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>-40</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>-40</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>If the Hip Press Misses the opponent, Jack-2 can chain into Sit Down extentions.</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>3be14565-e783-4db3-9168-bf98e290f21d</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>ce4da910-2232-4be6-a896-136d900764e1</t>
+        </is>
+      </c>
+    </row>
     <row r="96">
-      <c r="A96" s="1" t="inlineStr">
-        <is>
-          <t>Unblockable Arts</t>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>3+4</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>3+4</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Sit Down</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Sit Down</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>8ff726df-3bc4-4645-98be-c2fad557ee7d</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="inlineStr">
-        <is>
-          <t>Command</t>
-        </is>
-      </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>Command Full</t>
-        </is>
-      </c>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>Alt Commands</t>
-        </is>
-      </c>
-      <c r="D97" s="1" t="inlineStr">
-        <is>
-          <t>Alt Commands Full</t>
-        </is>
-      </c>
-      <c r="E97" s="1" t="inlineStr">
-        <is>
-          <t>Move Name</t>
-        </is>
-      </c>
-      <c r="F97" s="1" t="inlineStr">
-        <is>
-          <t>Move Name Full</t>
-        </is>
-      </c>
-      <c r="G97" s="1" t="inlineStr">
-        <is>
-          <t>To Stance</t>
-        </is>
-      </c>
-      <c r="H97" s="1" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="I97" s="1" t="inlineStr">
-        <is>
-          <t>Speed Full</t>
-        </is>
-      </c>
-      <c r="J97" s="1" t="inlineStr">
-        <is>
-          <t>Block Adv</t>
-        </is>
-      </c>
-      <c r="K97" s="1" t="inlineStr">
-        <is>
-          <t>Block Adv Full</t>
-        </is>
-      </c>
-      <c r="L97" s="1" t="inlineStr">
-        <is>
-          <t>Hit Adv</t>
-        </is>
-      </c>
-      <c r="M97" s="1" t="inlineStr">
-        <is>
-          <t>Hit Adv Full</t>
-        </is>
-      </c>
-      <c r="N97" s="1" t="inlineStr">
-        <is>
-          <t>Counter Hit Adv</t>
-        </is>
-      </c>
-      <c r="O97" s="1" t="inlineStr">
-        <is>
-          <t>Counter Hit Adv Full</t>
-        </is>
-      </c>
-      <c r="P97" s="1" t="inlineStr">
-        <is>
-          <t>Damage</t>
-        </is>
-      </c>
-      <c r="Q97" s="1" t="inlineStr">
-        <is>
-          <t>Damage Sum</t>
-        </is>
-      </c>
-      <c r="R97" s="1" t="inlineStr">
-        <is>
-          <t>Damage Full</t>
-        </is>
-      </c>
-      <c r="S97" s="1" t="inlineStr">
-        <is>
-          <t>Hit Range</t>
-        </is>
-      </c>
-      <c r="T97" s="1" t="inlineStr">
-        <is>
-          <t>Hit Range Full</t>
-        </is>
-      </c>
-      <c r="U97" s="1" t="inlineStr">
-        <is>
-          <t>Throw Type</t>
-        </is>
-      </c>
-      <c r="V97" s="1" t="inlineStr">
-        <is>
-          <t>Throw Escape</t>
-        </is>
-      </c>
-      <c r="W97" s="1" t="inlineStr">
-        <is>
-          <t>Properties</t>
-        </is>
-      </c>
-      <c r="X97" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="Y97" s="1" t="inlineStr">
-        <is>
-          <t>Taggable</t>
-        </is>
-      </c>
-      <c r="Z97" s="1" t="inlineStr">
-        <is>
-          <t>UUID</t>
-        </is>
-      </c>
-      <c r="AA97" s="1" t="inlineStr">
-        <is>
-          <t>ML UUID</t>
-        </is>
-      </c>
-      <c r="AB97" s="1" t="inlineStr">
-        <is>
-          <t>Parent UUID</t>
-        </is>
-      </c>
-      <c r="AC97" s="1" t="inlineStr">
-        <is>
-          <t>Unmatched</t>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>– ~3+4</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>3+4~3+4</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>– Hop Hip Press</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Sit Down – Hop Hip Press</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>-34</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>-34</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>-34</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>-34</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>-,35</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>-M</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>If the Hip Press Misses the opponent, Jack-2 can chain into Sit Down extentions.</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>1f37a24d-750f-4851-a2b5-a6b9a1b4ed26</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>hcf</t>
+          <t>– B</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>hcf</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>b,b+1</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>b,b+1</t>
+          <t>3+4,B</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Gigaton Start Up</t>
+          <t>– Roll Back</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gigaton Start Up</t>
+          <t>Sit Down – Roll Back</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -9045,49 +8841,54 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
+          <t>-,-</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>--</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>d1938783-b653-4c21-91d7-5303ce4b61cb</t>
+          <t>a96a391b-b0cf-493d-a205-6511f1e34903</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>67a32d45-116c-42ad-88df-89b38e4ca9aa</t>
+          <t>4f15e677-cb84-4d03-b6d8-82c26255c1d9</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>– b,db,d,df,f,uf,u,ub</t>
+          <t>– F</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>hcf,b,db,d,df,f,uf,u,ub</t>
+          <t>3+4,F</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>– Wind Up</t>
+          <t>– Roll Forward</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gigaton Start Up – Wind Up</t>
+          <t>Sit Down – Roll Forward</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -9115,482 +8916,836 @@
           <t>--</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>Can be repeated up to 5 times.</t>
-        </is>
-      </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>1f65d946-be2a-4bb4-9a27-18e4ad27b7a8</t>
+          <t>df8e44d6-d84c-4ee6-8117-15cb0b65ceb6</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>99aa8796-5bbe-4d4a-8523-9278daf2c772</t>
+          <t>0680a704-d8c9-47e5-91a9-98babe1c15af</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>d1938783-b653-4c21-91d7-5303ce4b61cb</t>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>–– 1</t>
+          <t>– 1,2,1,2</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>hcf,b,db,d,df,f,uf,u,ub,1</t>
+          <t>3+4,1,2,1,2</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>3+4,2,1,2,1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>–– Gigaton Punch</t>
+          <t>– Sitting Punches</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gigaton Start Up – Wind Up – Gigaton Punch</t>
+          <t>Sit Down – Sitting Punches</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>19</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-45 -43 -45 -43</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-45 -43 -45 -43</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-35 -32 -35 -32</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-35 -32 -35 -32</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-35 -32 -35 -32</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-35 -32 -35 -32</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
+          <t>10,10,10,10</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr">
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>-,10,10,10,10</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>llll</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>-llll</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>1e575213-1523-40b8-9492-0a92235d1799</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>71c8d35f-24b6-430d-abc5-2ff4c47a8f3b</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>KND d+1+2</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>KND d+1+2</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Spring Hammer - Sit Down</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Spring Hammer - Sit Down</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>+14</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>+14</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>+14</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>+14</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>9ea7e1a3-859f-438a-b3fc-0ff0de0e315f</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>0066d9e6-44cc-4c22-b95a-1c01b1cb1dcb</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>– 1,2,1,2</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>KND d+1+2,1,2,1,2</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>KND d+1+2,2,1,2,1</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>– Sitting Punches</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Spring Hammer - Sit Down – Sitting Punches</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>-45 -43 -45 -43</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>+20 -45 -43 -45 -43</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>-35 -32 -35 -32</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>+14 -35 -32 -35 -32</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>-35 -32 -35 -32</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>+14 -35 -32 -35 -32</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>10,10,10,10</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr">
-        <is>
-          <t>-,-,40</t>
-        </is>
-      </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>!</t>
-        </is>
-      </c>
-      <c r="T100" t="inlineStr">
-        <is>
-          <t>--!</t>
-        </is>
-      </c>
-      <c r="X100" t="inlineStr">
-        <is>
-          <t>Damage increases to 60, 80 and 199 with each extra Wind Up. Becomes Unblockable after 2 Wind Ups.</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>5effdb03-d23f-4671-8daa-b173c35d0ee4</t>
-        </is>
-      </c>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>8ae507ae-80ca-4f99-8564-71283564636c</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>1f65d946-be2a-4bb4-9a27-18e4ad27b7a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="101"/>
-    <row r="102">
-      <c r="A102" s="1" t="inlineStr">
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>12,10,10,10,10</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>llll</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>mllll</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>eb0c424e-d4b0-438e-bfb7-164bbca1894a</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>01e88eb2-b793-4ba3-9d87-7f7b3ab33381</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>9ea7e1a3-859f-438a-b3fc-0ff0de0e315f</t>
+        </is>
+      </c>
+    </row>
+    <row r="103"/>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>Unblockable Arts</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>Command</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t>Command Full</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>Alt Commands</t>
+        </is>
+      </c>
+      <c r="D105" s="1" t="inlineStr">
+        <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E105" s="1" t="inlineStr">
+        <is>
+          <t>Move Name</t>
+        </is>
+      </c>
+      <c r="F105" s="1" t="inlineStr">
+        <is>
+          <t>Move Name Full</t>
+        </is>
+      </c>
+      <c r="G105" s="1" t="inlineStr">
+        <is>
+          <t>To Stance</t>
+        </is>
+      </c>
+      <c r="H105" s="1" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="I105" s="1" t="inlineStr">
+        <is>
+          <t>Speed Full</t>
+        </is>
+      </c>
+      <c r="J105" s="1" t="inlineStr">
+        <is>
+          <t>Block Adv</t>
+        </is>
+      </c>
+      <c r="K105" s="1" t="inlineStr">
+        <is>
+          <t>Block Adv Full</t>
+        </is>
+      </c>
+      <c r="L105" s="1" t="inlineStr">
+        <is>
+          <t>Hit Adv</t>
+        </is>
+      </c>
+      <c r="M105" s="1" t="inlineStr">
+        <is>
+          <t>Hit Adv Full</t>
+        </is>
+      </c>
+      <c r="N105" s="1" t="inlineStr">
+        <is>
+          <t>Counter Hit Adv</t>
+        </is>
+      </c>
+      <c r="O105" s="1" t="inlineStr">
+        <is>
+          <t>Counter Hit Adv Full</t>
+        </is>
+      </c>
+      <c r="P105" s="1" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="Q105" s="1" t="inlineStr">
+        <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="R105" s="1" t="inlineStr">
+        <is>
+          <t>Damage Full</t>
+        </is>
+      </c>
+      <c r="S105" s="1" t="inlineStr">
+        <is>
+          <t>Hit Range</t>
+        </is>
+      </c>
+      <c r="T105" s="1" t="inlineStr">
+        <is>
+          <t>Hit Range Full</t>
+        </is>
+      </c>
+      <c r="U105" s="1" t="inlineStr">
+        <is>
+          <t>Throw Type</t>
+        </is>
+      </c>
+      <c r="V105" s="1" t="inlineStr">
+        <is>
+          <t>Throw Escape</t>
+        </is>
+      </c>
+      <c r="W105" s="1" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="X105" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="Y105" s="1" t="inlineStr">
+        <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Z105" s="1" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="AA105" s="1" t="inlineStr">
+        <is>
+          <t>ML UUID</t>
+        </is>
+      </c>
+      <c r="AB105" s="1" t="inlineStr">
+        <is>
+          <t>Parent UUID</t>
+        </is>
+      </c>
+      <c r="AC105" s="1" t="inlineStr">
+        <is>
+          <t>Unmatched</t>
+        </is>
+      </c>
+    </row>
+    <row r="106"/>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
         <is>
           <t>String Hit Arts</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="1" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
+      <c r="B108" s="1" t="inlineStr">
         <is>
           <t>Command Full</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>Alt Commands</t>
         </is>
       </c>
-      <c r="D103" s="1" t="inlineStr">
+      <c r="D108" s="1" t="inlineStr">
         <is>
           <t>Alt Commands Full</t>
         </is>
       </c>
-      <c r="E103" s="1" t="inlineStr">
+      <c r="E108" s="1" t="inlineStr">
         <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F103" s="1" t="inlineStr">
+      <c r="F108" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G103" s="1" t="inlineStr">
+      <c r="G108" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H103" s="1" t="inlineStr">
+      <c r="H108" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="I103" s="1" t="inlineStr">
+      <c r="I108" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="J103" s="1" t="inlineStr">
+      <c r="J108" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="K103" s="1" t="inlineStr">
+      <c r="K108" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="L103" s="1" t="inlineStr">
+      <c r="L108" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="M103" s="1" t="inlineStr">
+      <c r="M108" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="N103" s="1" t="inlineStr">
+      <c r="N108" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="O103" s="1" t="inlineStr">
+      <c r="O108" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="P103" s="1" t="inlineStr">
+      <c r="P108" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="Q103" s="1" t="inlineStr">
+      <c r="Q108" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="R103" s="1" t="inlineStr">
+      <c r="R108" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="S103" s="1" t="inlineStr">
+      <c r="S108" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="T103" s="1" t="inlineStr">
+      <c r="T108" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="U103" s="1" t="inlineStr">
+      <c r="U108" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="V103" s="1" t="inlineStr">
+      <c r="V108" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="W103" s="1" t="inlineStr">
+      <c r="W108" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="X103" s="1" t="inlineStr">
+      <c r="X108" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Y103" s="1" t="inlineStr">
+      <c r="Y108" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Z103" s="1" t="inlineStr">
+      <c r="Z108" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AA103" s="1" t="inlineStr">
+      <c r="AA108" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AB103" s="1" t="inlineStr">
+      <c r="AB108" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AC103" s="1" t="inlineStr">
+      <c r="AC108" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+    <row r="109">
+      <c r="A109" t="inlineStr">
         <is>
           <t>D+2,1,1,1,2,1,2,1,1+2,1+2</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>D+2,1,1,1,2,1,2,1,1+2,1+2</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr">
+      <c r="P109" t="inlineStr">
         <is>
           <t>10,6,5,7,7,6,6,8,21,25</t>
         </is>
       </c>
-      <c r="Q104" t="inlineStr">
+      <c r="Q109" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr">
+      <c r="R109" t="inlineStr">
         <is>
           <t>10,6,5,7,7,6,6,8,21,25</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr">
+      <c r="S109" t="inlineStr">
         <is>
           <t>sLLmmmmmmm</t>
         </is>
       </c>
-      <c r="T104" t="inlineStr">
+      <c r="T109" t="inlineStr">
         <is>
           <t>sLLmmmmmmm</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
+      <c r="Z109" t="inlineStr">
         <is>
           <t>cedd2a7b-61d7-42fe-9349-42a2b1503d3f</t>
         </is>
       </c>
-      <c r="AA104" t="inlineStr">
+      <c r="AA109" t="inlineStr">
         <is>
           <t>cedd2a7b-61d7-42fe-9349-42a2b1503d3f</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
+      <c r="AC109" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+    <row r="110">
+      <c r="A110" t="inlineStr">
         <is>
           <t>D+2,1,1,1,2,1,2,1,d+1+2,1+2</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>D+2,1,1,1,2,1,2,1,d+1+2,1+2</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr">
+      <c r="P110" t="inlineStr">
         <is>
           <t>10,6,5,7,7,6,6,8,12,35</t>
         </is>
       </c>
-      <c r="Q105" t="inlineStr">
+      <c r="Q110" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr">
+      <c r="R110" t="inlineStr">
         <is>
           <t>10,6,5,7,7,6,6,8,12,35</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr">
+      <c r="S110" t="inlineStr">
         <is>
           <t>sLLmmmmmlm</t>
         </is>
       </c>
-      <c r="T105" t="inlineStr">
+      <c r="T110" t="inlineStr">
         <is>
           <t>sLLmmmmmlm</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
+      <c r="Z110" t="inlineStr">
         <is>
           <t>46414757-6bbc-43ff-bcce-43bb3e815b75</t>
         </is>
       </c>
-      <c r="AA105" t="inlineStr">
+      <c r="AA110" t="inlineStr">
         <is>
           <t>46414757-6bbc-43ff-bcce-43bb3e815b75</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
+      <c r="AC110" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
+    <row r="111">
+      <c r="A111" t="inlineStr">
         <is>
           <t>uf+1,1,4,3,4,1,2,1,1+2,1+2</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>uf+1,1,4,3,4,1,2,1,1+2,1+2</t>
         </is>
       </c>
-      <c r="P106" t="inlineStr">
+      <c r="P111" t="inlineStr">
         <is>
           <t>15,8,5,5,5,8,6,8,21,25</t>
         </is>
       </c>
-      <c r="Q106" t="inlineStr">
+      <c r="Q111" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
-      <c r="R106" t="inlineStr">
+      <c r="R111" t="inlineStr">
         <is>
           <t>15,8,5,5,5,8,6,8,21,25</t>
         </is>
       </c>
-      <c r="S106" t="inlineStr">
+      <c r="S111" t="inlineStr">
         <is>
           <t>hmLLLmmmmm</t>
         </is>
       </c>
-      <c r="T106" t="inlineStr">
+      <c r="T111" t="inlineStr">
         <is>
           <t>hmLLLmmmmm</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
+      <c r="Z111" t="inlineStr">
         <is>
           <t>66ed2d10-6ef0-489d-ad01-ab4680052d18</t>
         </is>
       </c>
-      <c r="AA106" t="inlineStr">
+      <c r="AA111" t="inlineStr">
         <is>
           <t>66ed2d10-6ef0-489d-ad01-ab4680052d18</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr">
+      <c r="AC111" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+    <row r="112">
+      <c r="A112" t="inlineStr">
         <is>
           <t>uf+1,1,4,3,4,12,1,d+1+2,1+2</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>uf+1,1,4,3,4,12,1,d+1+2,1+2</t>
         </is>
       </c>
-      <c r="P107" t="inlineStr">
+      <c r="P112" t="inlineStr">
         <is>
           <t>15,8,5,5,5,8,6,8,12,35</t>
         </is>
       </c>
-      <c r="Q107" t="inlineStr">
+      <c r="Q112" t="inlineStr">
         <is>
           <t>107</t>
         </is>
       </c>
-      <c r="R107" t="inlineStr">
+      <c r="R112" t="inlineStr">
         <is>
           <t>15,8,5,5,5,8,6,8,12,35</t>
         </is>
       </c>
-      <c r="S107" t="inlineStr">
+      <c r="S112" t="inlineStr">
         <is>
           <t>hmLLLmmmlm</t>
         </is>
       </c>
-      <c r="T107" t="inlineStr">
+      <c r="T112" t="inlineStr">
         <is>
           <t>hmLLLmmmlm</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
+      <c r="Z112" t="inlineStr">
         <is>
           <t>bfdf582e-6190-406a-b25c-eee25e104050</t>
         </is>
       </c>
-      <c r="AA107" t="inlineStr">
+      <c r="AA112" t="inlineStr">
         <is>
           <t>bfdf582e-6190-406a-b25c-eee25e104050</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
+      <c r="AC112" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
